--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omkar Hajare\Desktop\download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omkar Hajare\Desktop\download\animatic-refinement\.claude\worktrees\romantic-jennings-5697e0\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{116BB515-0A8D-4A04-8CA4-7E9C3DF0E0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81167F0C-3A61-4EE9-BEB2-1EB1D5CFE9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{2B59BF26-7DE1-4D7C-8AD7-4A115391D9D5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="463">
   <si>
     <t>Node</t>
   </si>
@@ -72,144 +72,33 @@
     <t>Project Input &amp; Setup Interface</t>
   </si>
   <si>
-    <t>Capture all shot metadata and asset uploads from the artist/operator before the AI pipeline runs.</t>
-  </si>
-  <si>
-    <t>Client MP4 animatic (pre-broken into shots); hand-drawn character model sheets</t>
-  </si>
-  <si>
-    <t>metadata.json; uploaded MP4 shots; uploaded model sheet images</t>
-  </si>
-  <si>
-    <t>HTML + JS frontend; local/cloud storage</t>
-  </si>
-  <si>
-    <t>Single UI for per-shot + batch-level configuration.</t>
-  </si>
-  <si>
     <t>1A</t>
   </si>
   <si>
-    <t>HTML Form Design</t>
-  </si>
-  <si>
-    <t>Single-page form for per-shot metadata entry.</t>
-  </si>
-  <si>
     <t>User input</t>
   </si>
   <si>
-    <t>HTML form layout</t>
-  </si>
-  <si>
-    <t>HTML / CSS / JS</t>
-  </si>
-  <si>
-    <t>One row per shot; add/remove shot rows dynamically.</t>
-  </si>
-  <si>
     <t>1B</t>
   </si>
   <si>
-    <t>Form Fields</t>
-  </si>
-  <si>
-    <t>Capture Shot ID, Character Count, Character Identity, Character Position, Shot Duration @25FPS.</t>
-  </si>
-  <si>
     <t>Structured per-shot record</t>
   </si>
   <si>
     <t>HTML form controls</t>
   </si>
   <si>
-    <t>Position options: Exact Center / Center-Left / Center-Right / Left / Right. Duration in frames at 25 FPS.</t>
-  </si>
-  <si>
     <t>1C</t>
   </si>
   <si>
-    <t>MP4 Batch Upload UI</t>
-  </si>
-  <si>
-    <t>Multi-file upload for shot MP4s with preview thumbnails.</t>
-  </si>
-  <si>
-    <t>MP4 shot files</t>
-  </si>
-  <si>
-    <t>Uploaded MP4s keyed by Shot ID</t>
-  </si>
-  <si>
-    <t>HTML file input; FFmpeg thumbnailing</t>
-  </si>
-  <si>
-    <t>Must handle large batches; show per-file status.</t>
-  </si>
-  <si>
     <t>1D</t>
   </si>
   <si>
-    <t>Character Model Sheet Upload UI</t>
-  </si>
-  <si>
-    <t>One-time upload per project; multi-angle sheets stored keyed by character name.</t>
-  </si>
-  <si>
-    <t>Model sheet images (PNG/JPG)</t>
-  </si>
-  <si>
-    <t>Character asset library keyed by name</t>
-  </si>
-  <si>
-    <t>HTML file input</t>
-  </si>
-  <si>
-    <t>Accept multiple sheets per character (front, 3/4, profile, back).</t>
-  </si>
-  <si>
     <t>1E</t>
   </si>
   <si>
-    <t>Batch Size Configuration</t>
-  </si>
-  <si>
-    <t>Numeric input controlling how many shots RunPod processes per batch.</t>
-  </si>
-  <si>
-    <t>User input (integer)</t>
-  </si>
-  <si>
-    <t>batch_size value</t>
-  </si>
-  <si>
-    <t>HTML number input</t>
-  </si>
-  <si>
-    <t>Governs VRAM headroom on RunPod GPU.</t>
-  </si>
-  <si>
     <t>1F</t>
   </si>
   <si>
-    <t>Metadata Export</t>
-  </si>
-  <si>
-    <t>Writes a JSON/CSV pairing each MP4 with its metadata row.</t>
-  </si>
-  <si>
-    <t>Form state + uploaded files</t>
-  </si>
-  <si>
-    <t>metadata.json (canonical pipeline contract)</t>
-  </si>
-  <si>
-    <t>JS -&gt; JSON serializer</t>
-  </si>
-  <si>
-    <t>Hand-off file into Node 2.</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1411,6 +1300,132 @@
   </si>
   <si>
     <t>Part 1 only - ToonCrafter in-betweens handled in Part 2</t>
+  </si>
+  <si>
+    <t>Capture all shot metadata + character library before the AI pipeline runs. Static frontend, no server.</t>
+  </si>
+  <si>
+    <t>User input + character model sheet PNGs</t>
+  </si>
+  <si>
+    <t>metadata.json + characters.json + named sheet PNGs (browser-downloaded)</t>
+  </si>
+  <si>
+    <t>HTML + JS + localStorage</t>
+  </si>
+  <si>
+    <t>Locked: 1a (one big form, +Add shot blocks) + 2a (browser download) + 3a (separate Character Library page). MP4s are NOT uploaded by the form.</t>
+  </si>
+  <si>
+    <t>Character Library Page (characters.html)</t>
+  </si>
+  <si>
+    <t>Pre-register every character: upload 8-angle horizontal-strip model sheet + assign display name.</t>
+  </si>
+  <si>
+    <t>User input + sheet PNGs</t>
+  </si>
+  <si>
+    <t>characters.json + canonically-named sheet PNGs (downloaded)</t>
+  </si>
+  <si>
+    <t>Run once per project before the shot form. Persists to localStorage so the shot form's identity dropdown is populated.</t>
+  </si>
+  <si>
+    <t>Sheet-format quick check</t>
+  </si>
+  <si>
+    <t>Client-side validation: dimensions, horizontal-strip aspect ratio, alpha-island count ~8.</t>
+  </si>
+  <si>
+    <t>Uploaded sheet PNG</t>
+  </si>
+  <si>
+    <t>Pass/fail + warning shown on page</t>
+  </si>
+  <si>
+    <t>Canvas API</t>
+  </si>
+  <si>
+    <t>Full alpha-island slicing happens in Node 6; this is early-warning preview only.</t>
+  </si>
+  <si>
+    <t>Shot Metadata Form Page (index.html)</t>
+  </si>
+  <si>
+    <t>One big form with repeating '+ Add shot' blocks; one block per shot.</t>
+  </si>
+  <si>
+    <t>User input + character library from localStorage</t>
+  </si>
+  <si>
+    <t>In-memory shot list</t>
+  </si>
+  <si>
+    <t>HTML + JS</t>
+  </si>
+  <si>
+    <t>Prompts user to visit characters.html first if library is empty.</t>
+  </si>
+  <si>
+    <t>Per-shot fields</t>
+  </si>
+  <si>
+    <t>Capture Shot ID, MP4 filename, character count, per-character (identity dropdown, position L/CL/C/CR/R), duration in frames @25 FPS.</t>
+  </si>
+  <si>
+    <t>Identity dropdown sourced from characters.json/localStorage. MP4 file picker captures filename + thumbnail only - no upload.</t>
+  </si>
+  <si>
+    <t>Batch-level fields</t>
+  </si>
+  <si>
+    <t>Capture project_name, batch_size (RunPod VRAM control), operator notes.</t>
+  </si>
+  <si>
+    <t>Batch-level config object</t>
+  </si>
+  <si>
+    <t>batch_size feeds Node 11D VRAM monitoring.</t>
+  </si>
+  <si>
+    <t>metadata.json export (browser download)</t>
+  </si>
+  <si>
+    <t>Serialize form state to metadata.json and trigger browser download.</t>
+  </si>
+  <si>
+    <t>Form state</t>
+  </si>
+  <si>
+    <t>metadata.json file in user's Downloads</t>
+  </si>
+  <si>
+    <t>JS Blob + URL.createObjectURL + anchor download</t>
+  </si>
+  <si>
+    <t>Canonical hand-off contract into Node 2. No server, no POST.</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>Operator handoff workflow</t>
+  </si>
+  <si>
+    <t>Document manual steps to move downloaded files (metadata.json + characters.json + sheet PNGs + MP4s) into the pipeline input folder.</t>
+  </si>
+  <si>
+    <t>All Node 1 outputs</t>
+  </si>
+  <si>
+    <t>Pipeline input folder ready for Node 2</t>
+  </si>
+  <si>
+    <t>README in frontend/</t>
+  </si>
+  <si>
+    <t>Browser cannot write directly to disk; manual move is the bridge between frontend and pipeline.</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7804509-25BC-4BF9-AF8F-C9E70FD037F1}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" customWidth="1"/>
@@ -1909,19 +1924,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>421</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
+        <v>422</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>14</v>
+        <v>424</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>15</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -1929,25 +1944,25 @@
         <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>426</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>18</v>
+        <v>427</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>19</v>
+        <v>428</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>22</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -1955,25 +1970,25 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>24</v>
+        <v>431</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>25</v>
+        <v>432</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>26</v>
+        <v>434</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>27</v>
+        <v>435</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>28</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -1981,25 +1996,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>437</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>31</v>
+        <v>438</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>32</v>
+        <v>439</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>33</v>
+        <v>440</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>34</v>
+        <v>441</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>35</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2007,25 +2022,25 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>443</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>38</v>
+        <v>444</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>42</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2033,25 +2048,25 @@
         <v>9</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>44</v>
+        <v>446</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>45</v>
+        <v>447</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>47</v>
+        <v>448</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>49</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2059,77 +2074,77 @@
         <v>9</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>51</v>
+        <v>450</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>52</v>
+        <v>451</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>53</v>
+        <v>452</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>54</v>
+        <v>453</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>55</v>
+        <v>454</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>56</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>63</v>
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>70</v>
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2137,25 +2152,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2163,25 +2178,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2189,25 +2204,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2215,77 +2230,77 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>103</v>
+      <c r="A15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>9</v>
+      <c r="A16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2293,25 +2308,25 @@
         <v>9</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2319,25 +2334,25 @@
         <v>9</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2345,25 +2360,25 @@
         <v>9</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2371,77 +2386,77 @@
         <v>9</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>138</v>
+      <c r="A21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>144</v>
+      <c r="A22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2449,25 +2464,25 @@
         <v>9</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2475,25 +2490,25 @@
         <v>9</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2501,25 +2516,25 @@
         <v>9</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2527,77 +2542,77 @@
         <v>9</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>176</v>
+      <c r="A27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>183</v>
+      <c r="A28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2605,25 +2620,25 @@
         <v>9</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2631,25 +2646,25 @@
         <v>9</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>194</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2657,25 +2672,25 @@
         <v>9</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2683,25 +2698,25 @@
         <v>9</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2709,77 +2724,77 @@
         <v>9</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>219</v>
+      <c r="A34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>9</v>
+      <c r="A35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2787,22 +2802,22 @@
         <v>9</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>9</v>
@@ -2813,25 +2828,25 @@
         <v>9</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>236</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2839,25 +2854,25 @@
         <v>9</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2865,77 +2880,77 @@
         <v>9</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>248</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>255</v>
+      <c r="A40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>262</v>
+      <c r="A41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2943,25 +2958,25 @@
         <v>9</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2969,25 +2984,25 @@
         <v>9</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -2995,25 +3010,25 @@
         <v>9</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>9</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3021,25 +3036,25 @@
         <v>9</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>288</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3047,77 +3062,77 @@
         <v>9</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>289</v>
+        <v>246</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>294</v>
+        <v>245</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>302</v>
+      <c r="A47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>9</v>
+      <c r="A48" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3125,22 +3140,22 @@
         <v>9</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>9</v>
@@ -3151,22 +3166,22 @@
         <v>9</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>9</v>
@@ -3177,25 +3192,25 @@
         <v>9</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>323</v>
+        <v>210</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3203,77 +3218,77 @@
         <v>9</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>325</v>
+        <v>281</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>326</v>
+        <v>282</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>9</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>335</v>
+      <c r="A53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>9</v>
+      <c r="A54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3281,22 +3296,22 @@
         <v>9</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>343</v>
+        <v>124</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>9</v>
@@ -3307,25 +3322,25 @@
         <v>9</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>346</v>
+        <v>304</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>347</v>
+        <v>305</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>350</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3333,25 +3348,25 @@
         <v>9</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>9</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3359,77 +3374,77 @@
         <v>9</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>361</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>366</v>
+      <c r="A59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>371</v>
+      <c r="A60" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3437,25 +3452,25 @@
         <v>9</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>374</v>
+        <v>332</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>375</v>
+        <v>98</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>9</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3463,22 +3478,22 @@
         <v>9</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>381</v>
+        <v>65</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>9</v>
@@ -3489,25 +3504,25 @@
         <v>9</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>384</v>
+        <v>342</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>386</v>
+        <v>343</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>388</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3515,77 +3530,77 @@
         <v>9</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>391</v>
+        <v>347</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>124</v>
+        <v>350</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>394</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>400</v>
+      <c r="A65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>9</v>
+      <c r="A66" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3593,22 +3608,22 @@
         <v>9</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>406</v>
+        <v>364</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>407</v>
+        <v>365</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>408</v>
+        <v>366</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>410</v>
+        <v>368</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>411</v>
+        <v>39</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>9</v>
@@ -3619,25 +3634,25 @@
         <v>9</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>412</v>
+        <v>369</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>413</v>
+        <v>370</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>414</v>
+        <v>371</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>415</v>
+        <v>372</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>416</v>
+        <v>373</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>417</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3645,25 +3660,25 @@
         <v>9</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>419</v>
+        <v>376</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>421</v>
+        <v>378</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>422</v>
+        <v>379</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>423</v>
+        <v>39</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>424</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -3671,25 +3686,51 @@
         <v>9</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>425</v>
+        <v>381</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>426</v>
+        <v>382</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>427</v>
+        <v>383</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>428</v>
+        <v>384</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>76</v>
+        <v>386</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>430</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3708,10 +3749,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>431</v>
+        <v>394</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="66" x14ac:dyDescent="0.3">
@@ -3719,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>433</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="79.2" x14ac:dyDescent="0.3">
@@ -3727,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>434</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
@@ -3735,7 +3776,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>435</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
@@ -3743,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>436</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
@@ -3751,7 +3792,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>437</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="52.8" x14ac:dyDescent="0.3">
@@ -3759,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>438</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="66" x14ac:dyDescent="0.3">
@@ -3767,15 +3808,15 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="92.4" x14ac:dyDescent="0.3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -3786,52 +3827,52 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>432</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>444</v>
+        <v>407</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>446</v>
+        <v>409</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>448</v>
+        <v>411</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>449</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -3842,28 +3883,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>454</v>
+        <v>417</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="92.4" x14ac:dyDescent="0.3">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>457</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -1123,27 +1123,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Convert the rough animatic MP4 into individually-addressable frames.</t>
+          <t>Decode every queued rough-animatic MP4 into individually-addressable PNG frames (one folder per shot).</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Current shot MP4</t>
+          <t>queue.json (from Node 2)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>PNG sequence per shot</t>
+          <t>Per-shot frame folders + per-shot _manifest.json + aggregate node3_result.json; exit 0/1/2</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>FFmpeg</t>
+          <t>Python 3.13 (embedded locally, stdlib + imageio-ffmpeg on RunPod); no GPU imports</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Per-shot isolation; runs once per shot.</t>
+          <t>Locked: ffmpeg via imageio-ffmpeg wheel (no PATH dep); per-shot folders &lt;work&gt;/&lt;shotId&gt;/frame_NNNN.png; 1:1 decode (no -r); fail-fast on hard errors, warn-and-continue on frame-count drift; core logic in pipeline/node3.py + thin ComfyUI wrapper in custom_nodes/node_03_mp4_to_png/.</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1156,34 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Load MP4 shot</t>
+          <t>Load + validate queue.json</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Pull current shot from queue.</t>
+          <t>Read queue.json; confirm schemaVersion==1, every shot has shotId/mp4Path/durationFrames, no duplicate shotIds, every mp4Path exists on disk.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Processing queue</t>
+          <t>queue.json path</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Active MP4 path</t>
+          <t>Validated queue dict (or QueueInputError)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
+          <t>Python json + pathlib</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Loud failure on schema drift so Node 2 contract changes never silently half-run Node 3.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="4" t="inlineStr"/>
@@ -1190,32 +1194,32 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>FFmpeg PNG extraction at 25 FPS</t>
+          <t>Per-shot folder setup</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Decode shot into PNG sequence at 25 FPS.</t>
+          <t>Create &lt;work-dir&gt;/&lt;shotId&gt;/ and wipe any stale frame_*.png from prior partial runs.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>MP4 shot</t>
+          <t>work_dir path + shotId</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>PNG frames</t>
+          <t>Empty frames folder ready for ffmpeg</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>FFmpeg</t>
+          <t>Python pathlib</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Lossless PNG to preserve line-art edges.</t>
+          <t>Clean slate guarantees _manifest.json matches directory contents exactly.</t>
         </is>
       </c>
     </row>
@@ -1228,32 +1232,32 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Frame indexing</t>
+          <t>FFmpeg decode</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Filename convention shot_XXX_frame_YYY.png.</t>
+          <t>ffmpeg -y -hide_banner -loglevel error -i &lt;mp4&gt; -start_number 1 -vsync 0 &lt;out&gt;/frame_%04d.png. Non-zero exit -&gt; FFmpegError with stderr tail.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>PNG frames</t>
+          <t>MP4 path, empty out_dir</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Named PNG frames</t>
+          <t>frame_0001.png .. frame_NNNN.png</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>FFmpeg output pattern</t>
+          <t>imageio-ffmpeg (bundled binary)</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Zero-padded indices for sort stability.</t>
+          <t>No -r flag: rough MP4 is already 25 FPS; -r would resample. 1:1 decode is the contract.</t>
         </is>
       </c>
     </row>
@@ -1266,32 +1270,32 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Working directory storage</t>
+          <t>Frame-count check + sequence verify</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Isolated temp folder per shot.</t>
+          <t>Confirm 1..N contiguous numbering (gap -&gt; FrameExtractionError). Compare count to durationFrames; mismatch -&gt; FrameCountWarning (non-fatal).</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>PNG frames</t>
+          <t>frames folder; durationFrames from queue.json</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>/work/shot_XXX/</t>
+          <t>Pass / FrameExtractionError / FrameCountWarning record</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Filesystem</t>
+          <t>Python re + glob</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Keeps shots independent during batch.</t>
+          <t>Warn-and-continue: Node 9 will use the actual count when rebuilding timing.</t>
         </is>
       </c>
     </row>
@@ -1304,32 +1308,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Frame-count sanity check</t>
+          <t>Write manifests</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Verify extracted frame count matches metadata duration.</t>
+          <t>Write per-shot _manifest.json + top-level node3_result.json aggregating all shots + warnings. Node 4 reads node3_result.json.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>PNG frames; metadata duration</t>
+          <t>Accumulated ShotFrameResult + FrameCountWarning list</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Pass/fail flag + log</t>
+          <t>&lt;work-dir&gt;/&lt;shotId&gt;/_manifest.json + &lt;work-dir&gt;/node3_result.json</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Python json + dataclasses</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Log mismatch; do not halt batch.</t>
+          <t>CLI exit 0 success (warnings are exit 0), 1 Node3Error, 2 unexpected.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -1343,7 +1343,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Key Pose Extraction (Ignore Held Frames)</t>
@@ -1351,32 +1351,32 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Isolate only frames where the drawing actually changes.</t>
+          <t>Partition each shot into key poses (drawing actually changes) + held-frame runs (timing duplicates that do NOT go to the AI generator). Translation-aware: a character sliding across the frame without changing pose stays ONE key pose with per-held-frame (dy, dx) offsets.</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>PNG sequence</t>
+          <t>node3_result.json (from Node 3) + threshold (float) + max_edge (int)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Key pose frames + timing map</t>
+          <t>Per-shot keyposes/frame_NNNN.png copies + per-shot keypose_map.json + aggregate node4_result.json; exit 0/1/2</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Python + OpenCV / perceptual hashing</t>
+          <t>numpy (FFT phase correlation) + Pillow (PNG load + LANCZOS downscale); pure-Python, no GPU</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Held frames are NOT regenerated; only their timing is recorded.</t>
+          <t>Locked: phase correlation + aligned MAE (NOT naive pixel-diff); compare frame-vs-anchor not frame-vs-prev; downscale max edge=128; global threshold default 8.0; no min hold-length; key-pose PNGs COPIED preserving source filenames; core logic in pipeline/node4.py + thin ComfyUI wrapper in custom_nodes/node_04_keypose_extractor/.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
+      <c r="A23" s="4" t="n"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>4A</t>
@@ -1384,37 +1384,37 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Frame-by-frame difference analysis</t>
+          <t>Load + validate node3_result.json</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff or perceptual-hash between consecutive frames.</t>
+          <t>Check schemaVersion==1, required keys (workDir, shots), every shot has shotId/framesDir/frameFilenames, frames folder exists on disk. Raises Node3ResultInputError on any problem.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>PNG sequence</t>
+          <t>node3_result.json path</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Per-frame diff score</t>
+          <t>Validated dict (or Node3ResultInputError)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>OpenCV / imagehash</t>
+          <t>Python json + pathlib</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Perceptual hash is robust to minor noise.</t>
+          <t>Distinct from Node 3's QueueInputError so operator can tell "Node 3 never ran" from "Node 4 cannot consume what Node 3 wrote".</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="4" t="inlineStr"/>
+      <c r="A24" s="4" t="n"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>4B</t>
@@ -1422,75 +1422,75 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Threshold-based motion detection</t>
+          <t>Per-shot anchor walk + phase correlation</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Tunable threshold flags 'new pose' vs 'held'.</t>
+          <t>Frame 1 is the first key-pose anchor (downscaled grayscale). For frames 2..N: phase-correlate against the anchor via numpy FFT to estimate (dy_small, dx_small); compute aligned MAE over the valid overlap.</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Diff scores</t>
+          <t>Source frames dir; anchor (downscaled uint8 array); threshold; maxEdge</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Boolean flags per frame</t>
+          <t>(dy_small, dx_small, aligned_mae) per frame</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
+          <t>numpy.fft.fft2 + Pillow LANCZOS resample</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Compare vs current ANCHOR (not N-1) so held-frame offsets are cumulative-from-anchor, which is exactly what Node 9 replays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>4C</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Classify: held (translated) vs new key pose</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>If aligned MAE &lt;= threshold, frame is held (offset = [round(dy_small*scale), round(dx_small*scale)] in full-res pixels). Otherwise, frame becomes a new key pose and replaces the anchor.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Aligned MAE + (dy_small, dx_small) + downscale scale factor</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>HeldFrame or new KeyPoseEntry</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Threshold exposed as pipeline config.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>4C</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Unique key pose identification</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Extract frames representing distinct poses (e.g. point-A and point-B of a slide).</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Flagged frames</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>List of key pose frame indices</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Walk cycles: only extract the pose changes, not the slide.</t>
+          <t>No minimum hold-length filter. Even a 1-frame segment between two key poses is its own run.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="4" t="inlineStr"/>
+      <c r="A26" s="4" t="n"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>4D</t>
@@ -1498,37 +1498,37 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Timing map</t>
+          <t>Per-shot output: copy key-pose PNGs + write keypose_map.json</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>JSON mapping {key_pose_index: [held_frame_positions, held_duration]}.</t>
+          <t>Create &lt;shotId&gt;/keyposes/, wipe stale copies, shutil.copyfile each key-pose frame preserving source filename, write &lt;shotId&gt;/keypose_map.json describing the partition.</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Flag array</t>
+          <t>Per-shot KeyPoseEntry list; source frames dir</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>timing_map.json</t>
+          <t>&lt;shotId&gt;/keyposes/frame_NNNN.png copies + &lt;shotId&gt;/keypose_map.json {schemaVersion, shotId, totalFrames, sourceFramesDir, keyPosesDir, threshold, maxEdge, keyPoses: [{keyPoseIndex, sourceFrame, keyPoseFilename, heldFrames: [{frame, offset: [dy, dx]}]}]}</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Python json</t>
+          <t>Python shutil + json</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Consumed by Node 9 for reconstruction.</t>
+          <t>Source filenames preserved so Node 9 can cross-reference original frame numbers trivially.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="4" t="inlineStr"/>
+      <c r="A27" s="4" t="n"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>4E</t>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Export key pose frames</t>
+          <t>Aggregate result</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Save distinct key poses to /keyposes/ subfolder.</t>
+          <t>Write &lt;work-dir&gt;/node4_result.json: one ShotKeyPoseSummary per shot (shotId, totalFrames, keyPoseCount, sourceFramesDir, keyPosesDir, keyPoseMapPath) plus run-wide threshold + maxEdge. The contract Node 5 consumes.</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Key pose indices; PNG sequence</t>
+          <t>Accumulated ShotKeyPoseSummary list</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>/work/shot_XXX/keyposes/</t>
+          <t>&lt;work-dir&gt;/node4_result.json</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Python / shutil</t>
+          <t>Python json + dataclasses</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>These are the only frames fed into Node 7.</t>
+          <t>CLI exit 0 success, 1 Node4Error subclass, 2 unexpected.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -1579,27 +1579,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>For each key pose frame, determine which character is where and at what angle.</t>
+          <t>For each key pose, determine which character is where. Angle detection deferred to Node 6 (reference-sheet 8-angle matching).</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Key pose frames; metadata character list</t>
+          <t>node4_result.json (Node 4) + queue.json (Node 2) + min_area_ratio + merge_iou</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Per-character bounding box + position label + angle guess</t>
+          <t>Per-shot &lt;shotId&gt;/character_map.json + aggregate &lt;work-dir&gt;/node5_result.json; exit 0/1/2</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Vision model (SAM, YOLO) or heuristic silhouette detection</t>
+          <t>scipy.ndimage.label + binary_erosion (classical CC); numpy (Otsu); Pillow (PNG load). No ML, no GPU.</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Cross-validate counts against metadata.</t>
+          <t>Locked 2026-04-23: classical CC over ML (no 2GB download per pod; line-art doesn't fit ML training distribution); per-key-pose detection (not per-shot); position bins 25/20/10/20/25 split; Strategy A positional identity zip (v1); warn AND reconcile on count mismatch.</t>
         </is>
       </c>
     </row>
@@ -1612,32 +1612,32 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Analyze rough sketch frame</t>
+          <t>Load + validate inputs</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Vision pass - segmentation or silhouette detection.</t>
+          <t>Read node4_result.json + queue.json; check schemaVersion==1 + required keys; build shotId-&gt;[{identity, position}] lookup from queue.batches. Missing shotIds raise QueueLookupError.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Key pose PNG</t>
+          <t>node4_result.json path; queue.json path</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Masks / bounding boxes</t>
+          <t>Validated dicts + character lookup (or Node4ResultInputError / QueueLookupError)</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>SAM / custom segmenter</t>
+          <t>Python json + pathlib</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Rough sketches are low-detail; model must tolerate that.</t>
+          <t>Distinct from Node 4's Node3ResultInputError so operator can tell 'Node 4 never ran' from 'Node 5 cannot consume what Node 4 wrote'.</t>
         </is>
       </c>
     </row>
@@ -1650,30 +1650,34 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Detect character silhouettes / count</t>
+          <t>Per-key-pose connected-component detection</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Count characters in frame.</t>
+          <t>Load key-pose PNG as grayscale, apply Otsu binarization (foreground = dark ink), run scipy.ndimage.label with 8-connectivity, drop blobs below min_area_ratio*frame_area, merge bboxes with IoU&gt;=merge_iou.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Masks</t>
+          <t>Key-pose PNG path; min_area_ratio (default 0.001); merge_iou (default 0.5)</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Character count (int)</t>
+          <t>List of (x, y, w, h, area) bboxes + reconcile-dropped/reconcile-merged warnings</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
+          <t>numpy (Otsu inline); scipy.ndimage.label + find_objects</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>8-connectivity (diagonals count). Otsu is adaptive so paper/ink tone variation across shots is handled. IoU merge reunites floating details (eye drawn as separate blob) with parent silhouette.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="4" t="inlineStr"/>
@@ -1684,32 +1688,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Cross-validate with metadata character count</t>
+          <t>Reconcile count against metadata</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Flag mismatch between detected and declared counts.</t>
+          <t>Compare blob count to len(shot.characters). Too-many -&gt; keep top-N largest by area (count-mismatch-over warning). Too-few -&gt; progressive binary_erosion x1/x2/x3 until count matches (reconcile-eroded warning). Still-wrong -&gt; reconcile-failed warning; Node 6 fails cleanly.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Detected count; metadata count</t>
+          <t>Detected bboxes; expected count; binary mask</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Warning flag</t>
+          <t>Reconciled bboxes list + DetectionWarning records</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>scipy.ndimage.binary_erosion</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Log and continue; trust metadata on conflict.</t>
+          <t>Warn AND reconcile, never fail-fast (locked). Max 3 erosion iterations before giving up - beyond that we're eroding away legitimate character features.</t>
         </is>
       </c>
     </row>
@@ -1722,22 +1726,22 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Detect in-frame position</t>
+          <t>Position binning</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Classify each silhouette into L / CL / C / CR / R bins.</t>
+          <t>Compute each bbox's normalized centre-x and bucket into L/CL/C/CR/R via 25/20/10/20/25 thresholds: [0.00,0.25) L, [0.25,0.45) CL, [0.45,0.55) C, [0.55,0.75) CR, [0.75,1.00] R.</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Bounding boxes; frame width</t>
+          <t>Bbox list; frame width</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Position label per character</t>
+          <t>Per-bbox positionCode + centerX (normalized)</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -1747,7 +1751,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Fixed horizontal thirds-style bins.</t>
+          <t>C is a narrow 10% exact-centre band; L and R are 25% each. Same thresholds every shot - no operator knob.</t>
         </is>
       </c>
     </row>
@@ -1760,1422 +1764,1394 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Detect pose/angle</t>
+          <t>Identity assignment (Strategy A) + manifest write</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Estimate body angle (front / 3/4 / profile / back) per character.</t>
+          <t>Sort detections left-&gt;right by centre-x; sort metadata by position rank (L&lt;CL&lt;C&lt;CR&lt;R, tiebreak on metadata order); zip. Write &lt;shotId&gt;/character_map.json (next to keyposes/) + aggregate &lt;work-dir&gt;/node5_result.json.</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Masks</t>
+          <t>Bboxes + positions; shot.characters metadata list</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Angle label per character</t>
+          <t>&lt;shotId&gt;/character_map.json {schemaVersion, shotId, expectedCharacterCount, expectedCharacters, keyPoses:[{keyPoseIndex, sourceFrame, frameWidth, frameHeight, detections, warnings}]} + aggregate node5_result.json</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
+          <t>Python dataclasses + json</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Strategy A (positional) for v1. If real mismatch rates &gt; 5%, add v2 Strategy B (reference-sheet-similarity verification) as post-pass without replacing Strategy A. Extra unmatched bboxes carry identity='' for operator review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Character Reference Sheet Matching</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Pick the right view from the model sheet for each detected character.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Character identity + angle per key pose</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Reference crop per character per frame</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Python + image cropping</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>One-to-one mapping: identity -&gt; sheet -&gt; angle crop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Load character model sheets</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Load the sheet for each character named in metadata.</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Model sheet library</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>In-memory sheet images</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>PIL / openCV</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Identify required angle</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Use Node 5E output to know which view to fetch.</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Angle labels</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Angle selector per character</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Select closest matching reference view</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Pick front / 3-4 / profile / back from the sheet.</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Sheet + angle</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>Selected reference image</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>If exact angle missing, fall back to nearest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>6D</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Extract pose characteristics</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Capture arm position, gesture, expression cues from the rough sketch.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Rough key pose frame</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Pose hint tags / extracted pose skeleton</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
           <t>OpenPose / heuristic</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>Used by Node 6 for reference selection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>5F</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Multi-character disambiguation</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Match silhouettes to metadata identities by left-to-right ordering.</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Positions; metadata identities</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Character identity per silhouette</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Feeds Node 7A prompting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Prepare reference conditioning images</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Crop/normalize reference ready for IP-Adapter / Reference CN.</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Selected reference image</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Conditioning crops</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>PIL</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Resolution must match ComfyUI workflow input size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>AI-Powered Pose Refinement (Replace Rough With BnW Line Art)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Generate clean BnW line-art of the correct character in the same pose as the rough sketch.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Rough key pose frame + reference conditioning</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Refined BnW line-art key pose (per character)</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>ComfyUI + ControlNet + IP-Adapter + SD line-art checkpoint</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Core generative step. Seed-lock for consistency across frames.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>ControlNet conditioning</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Use rough sketch as pose/line-art control (Scribble / LineArt / OpenPose CN).</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Rough key pose</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>CN conditioning tensor</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ComfyUI ControlNet</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>LineArt or Scribble CN is best fit for rough animatic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Character consistency</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>IP-Adapter or Reference-Only CN with Node 6E reference.</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Reference conditioning</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Character-identity conditioning</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>ComfyUI IP-Adapter / Reference-Only CN</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Crucial for matching model sheet identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>7C</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Generate BnW line art</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Run SD checkpoint tuned for line-art.</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Combined conditioning</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Raw generated BnW image</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Stable Diffusion line-art model</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Lock sampler/seed settings across all frames of a shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>7D</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Enforce position per metadata</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Inpaint/compose so character lands in metadata position.</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Generated image; metadata position</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Positioned character image</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>ComfyUI compositor</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>7E</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Multi-character compositing</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Generate each character separately; composite onto one frame.</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Per-character outputs</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Combined frame</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>ComfyUI compositor</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Keeps each character identity clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>7F</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>QC gate</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Regenerate on identity drift, double-lines, or position offset.</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Generated frame</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Accepted frame or retry signal</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Heuristic / vision check</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Retry count capped by Node 11C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Scene Assembly (Per Key Pose Frame)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Produce the finished, fully-composed refined key pose frame.</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Per-character refined outputs</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>One clean composite PNG per key pose</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>PIL / ComfyUI compositor</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Output is still only key poses - held frames added in Node 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Place refined characters at correct positions</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Place on transparent/white canvas per metadata.</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Refined character images</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Composited canvas</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>PIL</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Scale matching</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Match the scale implied by the rough sketch.</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Rough sketch measurements</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Scaled composite</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>PIL</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>8C</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Handle multiple characters</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Preserve z-order from rough.</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Per-character layer stack</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>Ordered composite</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>PIL</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>8D</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>BnW line-art consistency</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Unify line weight / contrast across characters.</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Composited frame</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Normalized BnW frame</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>PIL / numpy</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Prevents jarring differences between characters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>8E</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Composite final refined key pose frames</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>One clean PNG per key pose.</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Composited frames</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>/work/shot_XXX/refined_keyposes/</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>PIL</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Timing Reconstruction (Re-apply Held Frames)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Rebuild the full-length sequence using the timing map from Node 4.</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Refined key poses; timing_map.json</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Full-length refined PNG sequence</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Required when a shot has &gt;1 character.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Character Reference Sheet Matching</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Pick the right view from the model sheet for each detected character.</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Character identity + angle per key pose</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Reference crop per character per frame</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Python + image cropping</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>One-to-one mapping: identity -&gt; sheet -&gt; angle crop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>6A</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Load character model sheets</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Load the sheet for each character named in metadata.</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Model sheet library</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>In-memory sheet images</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>PIL / openCV</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Identify required angle</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Use Node 5E output to know which view to fetch.</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Angle labels</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Angle selector per character</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>No new generation - just copies to match original timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="3" t="n"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Read timing map</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Load timing_map.json from Node 4D.</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>timing_map.json</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>In-memory map</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Python json</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Map new key poses to timing slots</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Each refined key pose inherits the same frame index its rough counterpart held.</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Refined key poses; timing map</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Frame-index plan</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>6C</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Select closest matching reference view</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Pick front / 3-4 / profile / back from the sheet.</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Sheet + angle</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Selected reference image</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="H55" s="6" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate refined frames for held durations</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Same-pose held frames are duplicated to match original timing.</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Refined key poses; held durations</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>Duplicated PNGs</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Python / shutil</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>No re-generation. Pure copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="4" t="n"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>9D</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Assemble complete PNG sequence</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Continuous numbering across the shot.</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Refined + duplicated frames</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Final PNG sequence</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>If exact angle missing, fall back to nearest.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>6D</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Extract pose characteristics</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Capture arm position, gesture, expression cues from the rough sketch.</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Rough key pose frame</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>Pose hint tags / extracted pose skeleton</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>OpenPose / heuristic</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Feeds Node 7A prompting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>6E</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Prepare reference conditioning images</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Crop/normalize reference ready for IP-Adapter / Reference CN.</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Selected reference image</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Conditioning crops</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Resolution must match ComfyUI workflow input size.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr"/>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>AI-Powered Pose Refinement (Replace Rough With BnW Line Art)</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Generate clean BnW line-art of the correct character in the same pose as the rough sketch.</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Rough key pose frame + reference conditioning</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Refined BnW line-art key pose (per character)</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>ComfyUI + ControlNet + IP-Adapter + SD line-art checkpoint</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Core generative step. Seed-lock for consistency across frames.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>7A</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ControlNet conditioning</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Use rough sketch as pose/line-art control (Scribble / LineArt / OpenPose CN).</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Rough key pose</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>CN conditioning tensor</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>ComfyUI ControlNet</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>LineArt or Scribble CN is best fit for rough animatic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="4" t="inlineStr"/>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Character consistency</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>IP-Adapter or Reference-Only CN with Node 6E reference.</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Reference conditioning</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Character-identity conditioning</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>ComfyUI IP-Adapter / Reference-Only CN</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Crucial for matching model sheet identity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>7C</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Generate BnW line art</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Run SD checkpoint tuned for line-art.</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Combined conditioning</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Raw generated BnW image</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Stable Diffusion line-art model</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>Lock sampler/seed settings across all frames of a shot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>7D</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Enforce position per metadata</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Inpaint/compose so character lands in metadata position.</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Generated image; metadata position</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Positioned character image</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>ComfyUI compositor</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="4" t="inlineStr"/>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>7E</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Multi-character compositing</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Generate each character separately; composite onto one frame.</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Per-character outputs</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Combined frame</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>ComfyUI compositor</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Keeps each character identity clean.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>7F</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>QC gate</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Regenerate on identity drift, double-lines, or position offset.</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Generated frame</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>Accepted frame or retry signal</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Heuristic / vision check</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Retry count capped by Node 11C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr"/>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Scene Assembly (Per Key Pose Frame)</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Produce the finished, fully-composed refined key pose frame.</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Per-character refined outputs</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>One clean composite PNG per key pose</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>PIL / ComfyUI compositor</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Output is still only key poses - held frames added in Node 9.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>8A</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Place refined characters at correct positions</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Place on transparent/white canvas per metadata.</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Refined character images</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Composited canvas</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Scale matching</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Match the scale implied by the rough sketch.</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Rough sketch measurements</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Scaled composite</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
-    </row>
-    <row r="51" ht="42" customHeight="1">
-      <c r="A51" s="4" t="inlineStr"/>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>8C</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Handle multiple characters</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Preserve z-order from rough.</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Per-character layer stack</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Ordered composite</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="4" t="inlineStr"/>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>8D</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>BnW line-art consistency</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Unify line weight / contrast across characters.</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Composited frame</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>Normalized BnW frame</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>PIL / numpy</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>Prevents jarring differences between characters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="4" t="inlineStr"/>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>8E</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Composite final refined key pose frames</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>One clean PNG per key pose.</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Composited frames</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>/work/shot_XXX/refined_keyposes/</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr"/>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Timing Reconstruction (Re-apply Held Frames)</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Rebuild the full-length sequence using the timing map from Node 4.</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>Refined key poses; timing_map.json</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Full-length refined PNG sequence</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="H57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>9E</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Verify total frame count</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Total frames must match metadata duration.</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>PNG sequence; metadata duration</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>Pass/fail flag</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>No new generation - just copies to match original timing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Read timing map</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Load timing_map.json from Node 4D.</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>timing_map.json</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>In-memory map</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Python json</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="42" customHeight="1">
-      <c r="A56" s="4" t="inlineStr"/>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>9B</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Map new key poses to timing slots</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Each refined key pose inherits the same frame index its rough counterpart held.</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Refined key poses; timing map</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Frame-index plan</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Hard check before encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Output Generation (PNG -&gt; MP4)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Encode the final refined PNG sequence back into an MP4.</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Final PNG sequence</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>shot_XXX_refined.mp4</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>FFmpeg</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>25 FPS to match source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>FFmpeg encoding</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>PNG sequence to MP4.</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>PNG sequence</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Raw MP4</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>FFmpeg</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Use high-quality codec (prores / h264 CRF low).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="4" t="n"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>25 FPS encoding</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Match source rate.</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>25 FPS MP4</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>FFmpeg</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="4" t="n"/>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Filename convention</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>shot_XXX_refined.mp4.</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>MP4</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Named output file</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>FFmpeg output argument</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="4" t="n"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>10D</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Output validation</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Duration, frame count, codec checks.</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Final MP4</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Validation report</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>ffprobe</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Hard check before marking shot done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="4" t="n"/>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>10E</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Archive working files</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Keep PNG sequence + intermediates for debugging / Part 2 reuse.</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Working folder</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>Archived /work/shot_XXX/</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Filesystem</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Part 2 (ToonCrafter) will need these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Batch Management</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Keep the pipeline moving shot-by-shot across the whole batch.</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Processing queue</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Completed batch + report</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Python orchestrator</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Runs across all shots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="3" t="n"/>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>11A</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Queue next shot</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>After current shot completes, pull the next.</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Queue state</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Active shot handoff</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="4" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>9C</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate refined frames for held durations</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Same-pose held frames are duplicated to match original timing.</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Refined key poses; held durations</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Duplicated PNGs</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Python / shutil</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>No re-generation. Pure copy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="4" t="inlineStr"/>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>9D</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Assemble complete PNG sequence</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Continuous numbering across the shot.</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>Refined + duplicated frames</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Final PNG sequence</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="H66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>11B</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Progress tracking &amp; logging</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Per-shot status, timing, errors.</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Pipeline events</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Log file / dashboard</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Python logging</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="4" t="n"/>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Error handling &amp; retry</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Configurable retries per failed node.</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Failure signals</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>Retry or fail-forward decision</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>9E</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Verify total frame count</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Total frames must match metadata duration.</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>PNG sequence; metadata duration</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Pass/fail flag</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Cap retries to avoid infinite loops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>11D</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>RunPod GPU / VRAM monitoring</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Pause or reduce batch if OOM risk.</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>nvidia-smi telemetry</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic batch adjustment</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>nvidia-smi / pynvml</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Protect against OOM crashes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="4" t="n"/>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>11E</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Final batch report</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Summary of successes, failures, per-shot runtime.</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>batch_report.json / html</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Hard check before encoding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="42" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Output Generation (PNG -&gt; MP4)</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Encode the final refined PNG sequence back into an MP4.</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Final PNG sequence</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>shot_XXX_refined.mp4</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>FFmpeg</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>25 FPS to match source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="42" customHeight="1">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>FFmpeg encoding</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>PNG sequence to MP4.</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>PNG sequence</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>Raw MP4</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>FFmpeg</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>Use high-quality codec (prores / h264 CRF low).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="42" customHeight="1">
-      <c r="A62" s="4" t="inlineStr"/>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>25 FPS encoding</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Match source rate.</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>25 FPS MP4</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>FFmpeg</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>10C</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Filename convention</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>shot_XXX_refined.mp4.</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Named output file</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>FFmpeg output argument</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="42" customHeight="1">
-      <c r="A64" s="4" t="inlineStr"/>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>10D</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Output validation</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Duration, frame count, codec checks.</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>Final MP4</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Validation report</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>ffprobe</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Hard check before marking shot done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="42" customHeight="1">
-      <c r="A65" s="4" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>10E</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Archive working files</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Keep PNG sequence + intermediates for debugging / Part 2 reuse.</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>Working folder</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>Archived /work/shot_XXX/</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Filesystem</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>Part 2 (ToonCrafter) will need these.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr"/>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Batch Management</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Keep the pipeline moving shot-by-shot across the whole batch.</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>Processing queue</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Completed batch + report</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Python orchestrator</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Runs across all shots.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="4" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>11A</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Queue next shot</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>After current shot completes, pull the next.</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Queue state</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>Active shot handoff</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>11B</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Progress tracking &amp; logging</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Per-shot status, timing, errors.</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Pipeline events</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>Log file / dashboard</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Python logging</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="4" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>11C</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Error handling &amp; retry</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Configurable retries per failed node.</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Failure signals</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>Retry or fail-forward decision</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>Cap retries to avoid infinite loops.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>11D</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>RunPod GPU / VRAM monitoring</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Pause or reduce batch if OOM risk.</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>nvidia-smi telemetry</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>Dynamic batch adjustment</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>nvidia-smi / pynvml</t>
-        </is>
-      </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Protect against OOM crashes.</t>
+          <t>Delivered alongside refined MP4s.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="4" t="inlineStr"/>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>11E</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Final batch report</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Summary of successes, failures, per-shot runtime.</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>Logs</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>batch_report.json / html</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>Delivered alongside refined MP4s.</t>
-        </is>
-      </c>
+      <c r="A71" s="4" t="n"/>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -1807,27 +1807,27 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Pick the right view from the model sheet for each detected character.</t>
+          <t>For each character Node 5 detected in each key pose, pick the best-matching 8-angle view from the model sheet and emit it as a BnW line-art crop ready for Node 7 IP-Adapter / Reference-Only conditioning.</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Character identity + angle per key pose</t>
+          <t>node5_result.json (Node 5) + queue.json (Node 2) + characters.json (Node 1) + sheet PNGs referenced from queue</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Reference crop per character per frame</t>
+          <t>Per-shot &lt;shotId&gt;/reference_map.json + &lt;shotId&gt;/reference_crops/&lt;identity&gt;_&lt;angle&gt;.png + _lineart.png + aggregate &lt;work-dir&gt;/node6_result.json</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Python + image cropping</t>
+          <t>Pillow (RGBA + alpha slicing) + scipy.ndimage (CC label) + numpy (Otsu + DoG + IoU/symmetry scoring); pure-Python, CPU-only</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>One-to-one mapping: identity -&gt; sheet -&gt; angle crop.</t>
+          <t>Locked 2026-04-23: require alpha on sheet (fail loud); canonical 8-angle order confirmed against Bhim template; structured-fail on angleOrderConfirmed=false; classical shape-similarity (IoU + symmetry + aspect + edge density) over ML; recompute silhouette in Node 6 (no Node 5 retro-change); DoG line-art (sigma1=1.0, sigma2=2.0); per-key-pose granularity; Option C thin ComfyUI wrapper; no new Python deps; characters.js now defaults angleOrderConfirmed=true.</t>
         </is>
       </c>
     </row>
@@ -1840,30 +1840,34 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Load character model sheets</t>
+          <t>Load + validate inputs</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Load the sheet for each character named in metadata.</t>
+          <t>Read node5_result.json + queue.json + characters.json. Check all schemaVersion==1. Build shotId -&gt; [{identity, sheetPath}] lookup. Enforce characters.conventions.angleOrderConfirmed==true (else AngleOrderUnconfirmedError). Raise Node5ResultInputError / QueueLookupError / CharactersInputError on malformed manifests or stale references.</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Model sheet library</t>
+          <t>node5_result.json path; queue.json path; characters.json path</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>In-memory sheet images</t>
+          <t>Validated dicts + character/sheet lookup (or typed Node6Error subclass)</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>PIL / openCV</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n"/>
+          <t>Python json + pathlib</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>QueueLookupError reused from Node 5 with identical semantics (same PipelineError root).</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="4" t="n"/>
@@ -1874,30 +1878,34 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Identify required angle</t>
+          <t>Slice + cache reference sheets</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Use Node 5E output to know which view to fetch.</t>
+          <t>Per unique identity: load sheetPath as RGBA; raise ReferenceSheetFormatError if not RGBA; scipy.ndimage.label on alpha&gt;0; verify bbox count==8 (else ReferenceSheetSliceError); cache crops keyed by (identity, angle_name) matching characters.conventions.angleOrderLeftToRight. Convert each color crop to line art via DoG (sigma1=1.0, sigma2=2.0, OR-combined with alpha boundary). Write color + line-art PNGs to &lt;shotId&gt;/reference_crops/&lt;identity&gt;_&lt;angle&gt;.png / _lineart.png.</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Angle labels</t>
+          <t>Sheet PNG per unique character; angle-name list from characters.json</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Angle selector per character</t>
+          <t>&lt;shotId&gt;/reference_crops/&lt;identity&gt;_&lt;angle&gt;.png + _lineart.png; in-memory (color, line-art) crop cache</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="n"/>
+          <t>Pillow (RGBA + alpha) + scipy.ndimage.label + numpy DoG</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Alpha channel is the authoritative silhouette; gating RGB-only sheets prevents Otsu fallback ambiguity.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="4" t="n"/>
@@ -1908,32 +1916,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Select closest matching reference view</t>
+          <t>Recompute silhouette per key-pose detection</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Pick front / 3-4 / profile / back from the sheet.</t>
+          <t>For each detection in every key-pose character_map.json: crop the key-pose PNG to the detection boundingBox; Otsu binarize; keep largest connected component as the rough silhouette mask.</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Sheet + angle</t>
+          <t>Key-pose PNG path + detection boundingBox</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Selected reference image</t>
+          <t>Binary silhouette mask per detection</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Pillow + numpy Otsu + scipy.ndimage.label</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>If exact angle missing, fall back to nearest.</t>
+          <t>Reuses the Otsu approach from Node 5 5B; edge case (Node 5 reconcile-eroded detections) tolerated given 8-way matching is coarse.</t>
         </is>
       </c>
     </row>
@@ -1946,32 +1954,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Extract pose characteristics</t>
+          <t>Angle matching (classical multi-signal score)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Capture arm position, gesture, expression cues from the rough sketch.</t>
+          <t>Scale-normalize rough silhouette + 8 reference alpha-silhouettes to a 128x128 centered-on-centroid canvas (aspect-preserving pad). Score each (rough, reference) pair via weighted combination of: silhouette IoU, horizontal-symmetry score, bbox aspect-ratio similarity, interior-edge density in upper head band. Pick max-score angle.</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Rough key pose frame</t>
+          <t>Rough silhouette mask + 8 reference silhouettes + original key-pose crop (for interior edges)</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Pose hint tags / extracted pose skeleton</t>
+          <t>Selected angle name + score breakdown per detection</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>OpenPose / heuristic</t>
+          <t>numpy + Pillow</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Feeds Node 7A prompting.</t>
+          <t>No ML/CLIP/pose-model in v1. Interior edge density breaks front/back silhouette tie (face lines present on front, absent on back). Weights + sigmas tuned at code-time against the Bhim smoke fixture.</t>
         </is>
       </c>
     </row>
@@ -1984,32 +1992,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Prepare reference conditioning images</t>
+          <t>Emit reference_map.json + aggregate node6_result.json</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Crop/normalize reference ready for IP-Adapter / Reference CN.</t>
+          <t>Per shot write &lt;shotId&gt;/reference_map.json: per key pose per detection {identity, selectedAngle, scoreBreakdown, referenceColorCropPath, referenceLineArtCropPath}. Aggregate &lt;work-dir&gt;/node6_result.json: one ShotReferenceSummary per shot (shotId, keyPoseCount, referenceMapPath, angleHistogram). Node 7 reads reference_map.json directly.</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Selected reference image</t>
+          <t>Accumulated per-key-pose angle selections + crop paths</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Conditioning crops</t>
+          <t>&lt;shotId&gt;/reference_map.json; &lt;work-dir&gt;/node6_result.json</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>PIL</t>
+          <t>Python json + dataclasses</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Resolution must match ComfyUI workflow input size.</t>
+          <t>CLI exit 0 success, 1 Node6Error subclass, 2 unexpected. reference_map.json is the contract Node 7 consumes.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>angleOrderConfirmed must still be False until Node 6 gets user confirmation of the 8-angle order.</t>
+          <t>angleOrderConfirmed defaults to True as of 2026-04-23 (canonical 8-angle order confirmed against Bhim template); Node 6 still hard-fails if an operator deliberately flips it False.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Locked: 1a (one big form, +Add shot blocks) + 2a (browser download) + 3a (separate Character Library page). MP4s are NOT uploaded by the form.</t>
+          <t>Locked: 1a (one big form, +Add shot blocks) + 2a (browser download) + 3a (separate Character Library page). MP4s are NOT uploaded by the form. Each character also carries a poseExtractor field (dwpose default / lineart-fallback for non-humans) for Node 7 routing.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Pre-register every character: upload 8-angle horizontal-strip model sheet + assign display name.</t>
+          <t>Pre-register every character: upload 8-angle horizontal-strip model sheet + assign display name + choose Node 7 pose extractor (dwpose default / lineart-fallback for non-humans like Jaggu).</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>characters.json + canonically-named sheet PNGs (downloaded)</t>
+          <t>characters.json + canonically-named sheet PNGs (downloaded) (each character entry carries poseExtractor).</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Locked: runs locally + on RunPod (run_node2.py wrapper); hard-fail whole batch on any error (no per-shot skip); pydantic v2 with extra='forbid'.</t>
+          <t>Locked: runs locally + on RunPod (run_node2.py wrapper); hard-fail whole batch on any error (no per-shot skip); pydantic v2 with extra='forbid'. Each queue.json per-character dict also carries poseExtractor (dwpose / lineart-fallback) from characters.json so Node 7 routes per-character without re-reading characters.json.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Load characters.json via pydantic (CharactersFile). Enforces non-empty list, bare sheetFilename, width/height &gt;= 1. Carries angleOrderConfirmed flag through for Node 6.</t>
+          <t>Load characters.json via pydantic (CharactersFile). Enforces non-empty list, bare sheetFilename, width/height &gt;= 1. Carries angleOrderConfirmed flag through for Node 6. Enforces each character's poseExtractor in {dwpose, lineart-fallback} (defaults to dwpose if absent so libraries saved before the field existed still load).</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2035,27 +2035,27 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Generate clean BnW line-art of the correct character in the same pose as the rough sketch.</t>
+          <t>Generate clean BnW line-art of the correct character in the same pose as the rough sketch. Pose comes from the rough (action-accurate) via DWPose (humans) or LineArt/Scribble fallback (non-humans). Identity comes from Node 6's color reference crop via IP-Adapter. Txt2img so rough pixels do not bleed through.</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Rough key pose frame + reference conditioning</t>
+          <t>node6_result.json + queue.json (for per-character poseExtractor) + Node 6's color reference crops + rough key-pose PNGs + pinned SD checkpoint / CN / IP-Adapter weights</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Refined BnW line-art key pose (per character)</t>
+          <t>Per-character refined BnW line-art PNGs on transparent background + per-shot refined_map.json + aggregate node7_result.json</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>ComfyUI + ControlNet + IP-Adapter + SD line-art checkpoint</t>
+          <t>ComfyUI workflow JSON + thin custom-node wrapper (breaks pipeline/node*.py template on purpose); SD 1.5 + AnyLoRA line-art checkpoint + optional BnW LoRA; DWPose preprocessor + DWPose CN; LineArt + Scribble CN (non-human fallback); IP-Adapter-Plus; RunPod-only</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Core generative step. Seed-lock for consistency across frames.</t>
+          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output.</t>
         </is>
       </c>
     </row>
@@ -2068,32 +2068,32 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>ControlNet conditioning</t>
+          <t>Load + validate inputs</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Use rough sketch as pose/line-art control (Scribble / LineArt / OpenPose CN).</t>
+          <t>Read node6_result.json + queue.json; check schemaVersion==1; build (shotId, keyPoseIndex, identity) -&gt; (referenceColorCropPath, poseExtractor) lookup. Raise Node6ResultInputError / QueueLookupError on manifest problems.</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Rough key pose</t>
+          <t>node6_result.json path; queue.json path</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>CN conditioning tensor</t>
+          <t>Validated dicts + per-detection routing table (or typed Node7Error subclass)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>ComfyUI ControlNet</t>
+          <t>Python json + pathlib</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>LineArt or Scribble CN is best fit for rough animatic.</t>
+          <t>Same validate-up-front pattern as Nodes 3/4/5/6 -- loud failure on schema drift.</t>
         </is>
       </c>
     </row>
@@ -2106,32 +2106,32 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Character consistency</t>
+          <t>Pose conditioning (per-character, routed)</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>IP-Adapter or Reference-Only CN with Node 6E reference.</t>
+          <t>Crop rough key-pose PNG to Node-5 bbox with margin. If poseExtractor=='dwpose': run DWPose preprocessor -&gt; skeleton -&gt; DWPose ControlNet at strength 0.75. If poseExtractor=='lineart-fallback': feed rough crop through LineArt + Scribble CN at strength 0.6 each instead.</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Reference conditioning</t>
+          <t>Rough key-pose PNG + Node-5 bbox + character poseExtractor route</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Character-identity conditioning</t>
+          <t>Pose CN conditioning tensor (skeleton or lineart/scribble)</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>ComfyUI IP-Adapter / Reference-Only CN</t>
+          <t>ComfyUI DWPose preprocessor + DWPose CN; LineArt CN; Scribble CN</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Crucial for matching model sheet identity.</t>
+          <t>DWPose handles stylized cartoon human proportions better than classical OpenPose. Quadrupeds (Jaggu) lack a reliable skeleton so they route through the lineart-fallback stack; every character still has a model sheet for identity.</t>
         </is>
       </c>
     </row>
@@ -2144,32 +2144,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Generate BnW line art</t>
+          <t>Identity conditioning (IP-Adapter)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Run SD checkpoint tuned for line-art.</t>
+          <t>Load Node 6's COLOR reference crop (not the DoG line-art) into IP-Adapter-Plus at strength 0.8. Reference-Only CN available as a secondary tiebreaker at lower priority.</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Combined conditioning</t>
+          <t>Node 6's referenceColorCropPath for (identity, angle)</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Raw generated BnW image</t>
+          <t>Identity conditioning tensor</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Stable Diffusion line-art model</t>
+          <t>ComfyUI IP-Adapter-Plus + Reference-Only CN</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Lock sampler/seed settings across all frames of a shot.</t>
+          <t>IP-Adapter expects a textured/colored image for its identity embedding; the DoG line-art crop is available for Reference-Only fallback but not the primary identity channel.</t>
         </is>
       </c>
     </row>
@@ -2182,30 +2182,34 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Enforce position per metadata</t>
+          <t>Generation (SD 1.5 + line-art checkpoint)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Inpaint/compose so character lands in metadata position.</t>
+          <t>SD 1.5 + AnyLoRA (line-art-tuned) + optional BnW LoRA. DPM++ 2M Karras, 25 steps, CFG 7.0, 512x512. Txt2img only -- no img2img bleed-through. Seed logged per (shotId, keyPoseIndex, identity) so a failed retry can be re-run deterministically.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Generated image; metadata position</t>
+          <t>Pose CN + Identity CN from 7B/7C</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Positioned character image</t>
+          <t>Raw generated RGB image</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>ComfyUI compositor</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="n"/>
+          <t>SD 1.5 + AnyLoRA line-art checkpoint + optional BnW LoRA</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Shot's multiple key poses share a seed base for visual coherence within the shot. Exact checkpoint + LoRA pinned in custom_nodes/node_07_pose_refiner/models.json + runpod_setup.sh.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="4" t="n"/>
@@ -2216,32 +2220,32 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Multi-character compositing</t>
+          <t>Post-process to BnW alpha PNG</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Generate each character separately; composite onto one frame.</t>
+          <t>Luminance-threshold the generated RGB to pure BnW; build alpha mask from the skeleton/lineart regions; write a transparent-background 512x512 PNG to &lt;shotId&gt;/refined/&lt;keyPoseIndex&gt;_&lt;identity&gt;.png.</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Per-character outputs</t>
+          <t>Raw generated RGB image</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Combined frame</t>
+          <t>&lt;shotId&gt;/refined/&lt;keyPoseIndex&gt;_&lt;identity&gt;.png</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>ComfyUI compositor</t>
+          <t>numpy + Pillow (luminance threshold + alpha build)</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Keeps each character identity clean.</t>
+          <t>Transparent-background output gives Node 8's compositor clean alpha to place each character onto the final frame canvas.</t>
         </is>
       </c>
     </row>
@@ -2254,32 +2258,32 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>QC gate</t>
+          <t>Emit manifest</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Regenerate on identity drift, double-lines, or position offset.</t>
+          <t>Write per-shot &lt;shotId&gt;/refined_map.json: every generated character (sourceKeyPoseFrame, identity, angle, seed, refinedPath, poseExtractor used, CN strengths). Aggregate &lt;work-dir&gt;/node7_result.json: ShotRefinedSummary per shot. Node 8 reads refined_map.json directly.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Generated frame</t>
+          <t>Accumulated generation records</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Accepted frame or retry signal</t>
+          <t>&lt;shotId&gt;/refined_map.json + &lt;work-dir&gt;/node7_result.json</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Heuristic / vision check</t>
+          <t>Python json + dataclasses</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Retry count capped by Node 11C.</t>
+          <t>CLI exit 0 success (per-generation skips are still exit 0), 1 Node7Error subclass, 2 unexpected. No auto-retry / QC gate in v1 -- metadata only; retries are a future Node 11C hook.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2055,7 +2055,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output.</t>
+          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack).</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2055,7 +2055,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack).</t>
+          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Same validate-up-front pattern as Nodes 3/4/5/6 -- loud failure on schema drift.</t>
+          <t>Same validate-up-front pattern as Nodes 3/4/5/6 -- loud failure on schema drift. Shipped in pipeline/cli_node7.main + custom_nodes/node_07_pose_refiner/orchestrate.py (load_node6_result + load_queue + build_pose_extractor_lookup + build_routing_table).</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>DWPose handles stylized cartoon human proportions better than classical OpenPose. Quadrupeds (Jaggu) lack a reliable skeleton so they route through the lineart-fallback stack; every character still has a model sheet for identity.</t>
+          <t>DWPose handles stylized cartoon human proportions better than classical OpenPose. Quadrupeds (Jaggu) lack a reliable skeleton so they route through the lineart-fallback stack; every character still has a model sheet for identity. Shipped via two workflow JSON templates routed per-detection by orchestrate.py: workflow.json (DWPose: nodes 40 DWPreprocessor + 41 ControlNetApplyAdvanced @ 0.75 + 42 ControlNetLoader control_v11p_sd15_openpose.pth) vs workflow_lineart_fallback.json (LineArtPreprocessor + Scribble CN stack @ 0.6 each).</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>IP-Adapter expects a textured/colored image for its identity embedding; the DoG line-art crop is available for Reference-Only fallback but not the primary identity channel.</t>
+          <t>IP-Adapter expects a textured/colored image for its identity embedding; the DoG line-art crop is available for Reference-Only fallback but not the primary identity channel. Shipped in both workflow templates: IPAdapterUnifiedLoader node 50 (PLUS high strength) + IPAdapter node 51 @ weight 0.8 fed from node 12 LoadImage (Node 6 color reference crop).</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Shot's multiple key poses share a seed base for visual coherence within the shot. Exact checkpoint + LoRA pinned in custom_nodes/node_07_pose_refiner/models.json + runpod_setup.sh.</t>
+          <t>Shot's multiple key poses share a seed base for visual coherence within the shot. Exact checkpoint + LoRA pinned in custom_nodes/node_07_pose_refiner/models.json + runpod_setup.sh. Shipped in both workflow templates: node 3 KSampler with DPM++ 2M Karras, 25 steps, CFG 7.0, 512x512 EmptyLatentImage (node 5). Seed derived deterministically from SHA256(project|shotId|keyPoseIndex|identity) masked to 31 bits (orchestrate._derive_seed).</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Transparent-background output gives Node 8's compositor clean alpha to place each character onto the final frame canvas.</t>
+          <t>Transparent-background output gives Node 8's compositor clean alpha to place each character onto the final frame canvas. Shipped in both workflow templates: node 20 SaveImage with filename_prefix animatic/refined; orchestrate.extract_first_image downloads the PNG via ComfyUI /view and writes to &lt;shotId&gt;/refined/&lt;NNN&gt;_&lt;identity&gt;.png.</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>CLI exit 0 success (per-generation skips are still exit 0), 1 Node7Error subclass, 2 unexpected. No auto-retry / QC gate in v1 -- metadata only; retries are a future Node 11C hook.</t>
+          <t>CLI exit 0 success (per-generation skips are still exit 0), 1 Node7Error subclass, 2 unexpected. No auto-retry / QC gate in v1 -- metadata only; retries are a future Node 11C hook. Shipped in custom_nodes/node_07_pose_refiner/manifest.py: write_refined_map (per-shot) + write_node7_result (aggregate, stamps refinedAt UTC). Dry-run marks every generation status=skipped; live run marks failures status=error and CLI still exits 0.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2055,7 +2055,8 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).</t>
+          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).
+Status (2026-04-25): DONE - live-verified on RunPod. First live run: 2 generated / 0 skipped / 0 error, 36s, lineart-fallback route, 2-character synthetic smoke fixture. DWPose route shipped but not yet exercised. Bringup notes for the runpod-slim pod image: tools/POD_NOTES_runpod_slim.md.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2055,8 +2055,9 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).
-Status (2026-04-25): DONE - live-verified on RunPod. First live run: 2 generated / 0 skipped / 0 error, 36s, lineart-fallback route, 2-character synthetic smoke fixture. DWPose route shipped but not yet exercised. Bringup notes for the runpod-slim pod image: tools/POD_NOTES_runpod_slim.md.</t>
+          <t xml:space="preserve">Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).
+Status (2026-04-25): DONE - both routes live-verified on RunPod. First live run (lineart-fallback both characters): 2 generated / 0 skipped / 0 error, 36s wall time, 2-character synthetic smoke fixture. DWPose verification (same fixture, Bhim flipped to dwpose, Jaggu still lineart-fallback): 2 generated / 0 skipped / 0 error, 41s wall time, both routes in the same Node 7 invocation; per-character routing table works; Bhim PNG bytes differ from baseline (sha d77d9b18.. vs 038f69e6..) confirming DWPose contributes pose info; Jaggu PNG bytes are bit-identical (sha 5aa3c619..) confirming the deterministic-seed contract holds for unchanged routes. Runpod-slim pod image needed FOUR bringup steps (symlink comfyui_controlnet_aux, write extra_model_paths.yaml, add weight_type: standard to both workflow JSONs, pip-install matplotlib + scikit-image + onnxruntime into the venv for DWPose) - all captured in tools/POD_NOTES_runpod_slim.md and the Node 7 - live-run addendum of CLAUDE.md.
+</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2323,7 +2323,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Output is still only key poses - held frames added in Node 9.</t>
+          <t>Status (2026-04-25): Design locked. The bbox is the single source of truth for character placement (Node 5 wrote it, Node 7 cropped with it, Node 8 places with it). Feet-pinned scaling: paste refined 512x512 onto canvas centered on (bbox.centerX, bbox.bottomY), scale by bbox.height / character_height_in_512. Output canvas = source MP4 resolution exactly. Solid white background. Z-order by bbox.bottomY descending. BnW threshold only, no stroke-width normalize in v1. Substitute-rough on Node 7 errors (warn-and-reconcile, not fail-loud). Pipeline Option-C template (pipeline/node8.py + thin ComfyUI wrapper). Pure-Python PIL+numpy, GPU-agnostic. No new deps. CLI: run_node8.py --node7-result &lt;path&gt;. Output is still only key poses — held frames added in Node 9.</t>
         </is>
       </c>
     </row>
@@ -2341,25 +2341,29 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Place on transparent/white canvas per metadata.</t>
+          <t>Load + validate node7_result.json (schemaVersion==1). For each shot chase pointers to refined_map.json, character_map.json (Node 5), keypose_map.json (Node 4). Probe one frame_NNNN.png per shot for original (W, H).</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Refined character images</t>
+          <t>node7_result.json (--node7-result path); per-shot refined/character/keypose maps; one Node 3 frame for dims</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Composited canvas</t>
+          <t>Validated in-memory shot list with bboxes, refined PNG paths, source frame dims</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="n"/>
+          <t>Python stdlib (json), PIL (probe dims)</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Raises Node7ResultInputError on any structural problem. Locked decision #1 (bbox = single source of truth).</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="4" t="n"/>
@@ -2370,30 +2374,34 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Scale matching</t>
+          <t>Per-key-pose canvas build</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Match the scale implied by the rough sketch.</t>
+          <t>Create (W, H) RGB white canvas per key pose, where (W, H) is the source MP4 resolution probed in 8A.</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Rough sketch measurements</t>
+          <t>Source frame dims from 8A</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Scaled composite</t>
+          <t>Blank RGB white canvas per key pose, ready for character paste</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="n"/>
+          <t>PIL.Image.new</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Locked decisions #3 (canvas = source MP4 res) + #4 (background = solid white).</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="4" t="n"/>
@@ -2404,30 +2412,34 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Handle multiple characters</t>
+          <t>Per-character paste (feet-pinned)</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Preserve z-order from rough.</t>
+          <t>For each character with status==ok: open 512x512 refined PNG, find lowest non-white pixel = feet_y_in_512, compute scale = bbox.height / (feet_y_in_512 - top_y_in_512), resize aspect-preserving, threshold to BnW, paste centered on (bbox.centerX, bbox.bottomY). For status!=ok: copy rough key-pose pixels in the bbox region (substitute-rough) + warn.</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Per-character layer stack</t>
+          <t>Refined 512x512 PNGs (Node 7), Node 5 bboxes, rough key-pose PNG (Node 3/4) for substitute fallback</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Ordered composite</t>
+          <t>Characters pasted onto the canvas; warnings for any substitute-rough events</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="n"/>
+          <t>PIL (open, resize, paste, threshold), numpy (find non-white pixel)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Locked decisions #2 (feet-pinned scaling, NOT stretch-to-fit) + #6 (BnW threshold only) + #7 (substitute-rough on Node 7 errors).</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="4" t="n"/>
@@ -2438,32 +2450,32 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>BnW line-art consistency</t>
+          <t>Z-order resolution</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Unify line weight / contrast across characters.</t>
+          <t>Sort detections per key pose by bbox.bottomY ascending and paste in that order so lower-on-screen characters land last (drawn on top).</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Composited frame</t>
+          <t>Per-key-pose detection list with bboxes</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Normalized BnW frame</t>
+          <t>Z-ordered paste sequence (input to 8C)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>PIL / numpy</t>
+          <t>Python sorted(), no deps</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Prevents jarring differences between characters.</t>
+          <t>Locked decision #5 (z-order = bbox.bottomY descending). 8D actually feeds 8C — the order they're listed is editorial; the code does z-sort then paste.</t>
         </is>
       </c>
     </row>
@@ -2476,30 +2488,34 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Composite final refined key pose frames</t>
+          <t>Emit composed PNGs + manifests</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>One clean PNG per key pose.</t>
+          <t>Write &lt;shotId&gt;/composed/&lt;keyPoseIndex&gt;_composite.png (RGB, source MP4 res, white bg, no alpha), per-shot composed_map.json, and the aggregate &lt;work-dir&gt;/node8_result.json.</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Composited frames</t>
+          <t>Composited canvas from 8B+8C+8D</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>/work/shot_XXX/refined_keyposes/</t>
+          <t>&lt;shotId&gt;/composed/*_composite.png + composed_map.json + node8_result.json</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>PIL</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="n"/>
+          <t>PIL (save), Python json</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Locked consequences: composed_map.json is Node 9's contract. Output is RGB no-alpha. Rerun wipes &lt;shotId&gt;/composed/ first so manifest always matches dir exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="4" t="inlineStr">

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2323,7 +2323,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Status (2026-04-25): Design locked. The bbox is the single source of truth for character placement (Node 5 wrote it, Node 7 cropped with it, Node 8 places with it). Feet-pinned scaling: paste refined 512x512 onto canvas centered on (bbox.centerX, bbox.bottomY), scale by bbox.height / character_height_in_512. Output canvas = source MP4 resolution exactly. Solid white background. Z-order by bbox.bottomY descending. BnW threshold only, no stroke-width normalize in v1. Substitute-rough on Node 7 errors (warn-and-reconcile, not fail-loud). Pipeline Option-C template (pipeline/node8.py + thin ComfyUI wrapper). Pure-Python PIL+numpy, GPU-agnostic. No new deps. CLI: run_node8.py --node7-result &lt;path&gt;. Output is still only key poses — held frames added in Node 9.</t>
+          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node8.py + pipeline/cli_node8.py + run_node8.py + custom_nodes/node_08_scene_assembler/__init__.py + tests/test_node8.py (51 tests pass, 258 repo-wide). Pure-Python PIL+numpy, no GPU, no new deps. Bbox is single source of truth (Node 5 wrote, Node 7 cropped, Node 8 places back). Feet-pinned scaling: feet land at bbox.bottomY within +/-2 px LANCZOS tolerance, never in the bbox middle. White canvas at source MP4 res, z-order by bbox.bottomY ascending, BnW threshold (no dilate/erode normalize in v1). Substitute-rough fallback on Node 7 status=error or empty-refined-PNG: warn and exit 0; only an unfillable slot (refined dead AND rough also dead) raises RefinedPngError. Rerun wipes &lt;shotId&gt;/composed/ first. Output is still only key poses - held frames added in Node 9.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>No new generation - just copies to match original timing.</t>
+          <t>Status (2026-04-25): Design locked. Translate-and-copy on a fresh white canvas - NO AI on held frames (Node 4's whole reason for going translation-aware). For every frame in the original timeline: anchor frame = copy Node 8 composite as-is; held frame = paste Node 8 composite at offset (dx, dy) from keypose_map.json onto fresh white canvas, exposed regions stay white. Whole-frame translation (not per-character; that property is baked into Node 8's composite already). Output canvas = source MP4 res. Output frame numbering = 1-indexed 4-digit frame_NNNN.png so Node 10 can ffmpeg-glob. CLI: run_node9.py --node8-result &lt;path&gt; only (chases composed_map.json -&gt; shot root -&gt; keypose_map.json). Fail-loud on missing composed PNG and on totalFrames mismatch. Off-canvas translates are NOT errors (mathematically valid for end-of-slide shots). Pipeline Option-C template (pipeline/node9.py + thin ComfyUI wrapper). Pure-Python PIL+numpy, GPU-agnostic, no new deps.</t>
         </is>
       </c>
     </row>
@@ -2564,30 +2564,34 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Read timing map</t>
+          <t>Load + validate inputs</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Load timing_map.json from Node 4D.</t>
+          <t>Read node8_result.json (schemaVersion==1), chase pointers to per-shot composed_map.json + sibling keypose_map.json. Validate Node 4 invariants: every frame index appears exactly once, all in [1, totalFrames], no duplicate keyPoseIndices.</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>timing_map.json</t>
+          <t>node8_result.json (--node8-result); per-shot composed_map.json; per-shot keypose_map.json</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>In-memory map</t>
+          <t>Validated in-memory shot list with per-frame (keyPoseIndex, offset, isAnchor) lookup</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Python json</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="n"/>
+          <t>Python stdlib (json, pathlib)</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Raises Node8ResultInputError or KeyPoseMapInputError on structural problems. Locked decisions #6 (single --node8-result) + #10 (duplicate frame index = hard error).</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="4" t="n"/>
@@ -2598,30 +2602,34 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Map new key poses to timing slots</t>
+          <t>Map key poses to timing slots</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Each refined key pose inherits the same frame index its rough counterpart held.</t>
+          <t>Build per-shot frame_index -&gt; (keyPoseIndex, offset_dy_dx, isAnchor) lookup so each frame resolves directly to source composite + translation in O(1).</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Refined key poses; timing map</t>
+          <t>Validated keypose_map.json from 9A</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Frame-index plan</t>
+          <t>Per-frame source-composite + offset lookup table</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="n"/>
+          <t>Python dict</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Pure data-shape transform; no I/O.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="4" t="n"/>
@@ -2632,32 +2640,32 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Duplicate refined frames for held durations</t>
+          <t>Translate-and-copy per frame</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Same-pose held frames are duplicated to match original timing.</t>
+          <t>For each frame_index in 1..totalFrames: open source composite (cached per keyPoseIndex within a shot), build fresh white canvas at composite's (W, H), paste composite at offset (dx, dy). Anchor frames (offset==[0,0]) are bit-identical copies of Node 8's composite.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Refined key poses; held durations</t>
+          <t>Per-frame lookup from 9B; Node 8 composite PNGs from &lt;shot&gt;/composed/</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Duplicated PNGs</t>
+          <t>&lt;shot&gt;/timed/frame_NNNN.png (RGB, source MP4 res, white bg)</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Python / shutil</t>
+          <t>PIL.Image.new + paste; per-keyPoseIndex composite cache</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>No re-generation. Pure copy.</t>
+          <t>Locked decisions #1 (translate-and-copy on white canvas, NO AI), #2 (whole-frame translation, not per-character), #4 (white fill), #9 (off-canvas translates are NOT errors).</t>
         </is>
       </c>
     </row>
@@ -2670,30 +2678,34 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Assemble complete PNG sequence</t>
+          <t>Assemble + verify</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Continuous numbering across the shot.</t>
+          <t>Count &lt;shot&gt;/timed/frame_*.png files; must equal keypose_map.totalFrames. Mismatch raises FrameCountMismatchError with shot ID + expected/actual counts.</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Refined + duplicated frames</t>
+          <t>&lt;shot&gt;/timed/ directory + keypose_map.totalFrames</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Final PNG sequence</t>
+          <t>Per-shot pass/fail check; raises on mismatch</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n"/>
+          <t>Path.glob</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Locked decision #8 (totalFrames mismatch is a hard error). Defends against silent Node 4 bugs.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="4" t="n"/>
@@ -2704,32 +2716,32 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Verify total frame count</t>
+          <t>Emit manifests</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Total frames must match metadata duration.</t>
+          <t>Write &lt;shotId&gt;/timed_map.json (per-frame record: frameIndex, sourceKeyPoseIndex, offset, composedSourcePath, timedPath, isAnchor) and aggregate &lt;work-dir&gt;/node9_result.json (per-shot summary).</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>PNG sequence; metadata duration</t>
+          <t>Outputs from 9C + 9D</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Pass/fail flag</t>
+          <t>&lt;shotId&gt;/timed_map.json + node9_result.json</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Python json</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Hard check before encoding.</t>
+          <t>timed_map.json is Node 10's contract. Rerun wipes &lt;shot&gt;/timed/ first so the manifest always matches the dir exactly. Locked decisions #5 (1-indexed 4-digit numbering) + #13 (rerun safety).</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2551,7 +2551,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Status (2026-04-25): Design locked. Translate-and-copy on a fresh white canvas - NO AI on held frames (Node 4's whole reason for going translation-aware). For every frame in the original timeline: anchor frame = copy Node 8 composite as-is; held frame = paste Node 8 composite at offset (dx, dy) from keypose_map.json onto fresh white canvas, exposed regions stay white. Whole-frame translation (not per-character; that property is baked into Node 8's composite already). Output canvas = source MP4 res. Output frame numbering = 1-indexed 4-digit frame_NNNN.png so Node 10 can ffmpeg-glob. CLI: run_node9.py --node8-result &lt;path&gt; only (chases composed_map.json -&gt; shot root -&gt; keypose_map.json). Fail-loud on missing composed PNG and on totalFrames mismatch. Off-canvas translates are NOT errors (mathematically valid for end-of-slide shots). Pipeline Option-C template (pipeline/node9.py + thin ComfyUI wrapper). Pure-Python PIL+numpy, GPU-agnostic, no new deps.</t>
+          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node9.py + pipeline/cli_node9.py + run_node9.py + custom_nodes/node_09_timing_reconstructor/__init__.py + tests/test_node9.py (42 tests pass, 300 repo-wide). Pure-Python PIL+numpy, no GPU, no new deps. Translate-and-copy on a fresh white canvas: anchor frames are bit-identical pixel copies of Node 8's composite; held frames are pasted at (dx, dy) offset from keypose_map.json onto fresh white canvas, exposed regions stay white. Whole-frame translation (per-character placement is already baked into Node 8's composite). Off-canvas translates are NOT errors (mathematically valid for end-of-slide shots; produces mostly-white frame). Hard-fails on missing composed PNG (TimingReconstructionError), totalFrames mismatch (FrameCountMismatchError), and Node 4 invariant violations like duplicate frame indices or out-of-range frames (KeyPoseMapInputError). Rerun wipes &lt;shot&gt;/timed/ first. CLI: --node8-result only (chases composed_map.json -&gt; shot root -&gt; keypose_map.json). Output is full per-frame sequence ready for Node 10 to encode back to MP4.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>25 FPS to match source.</t>
+          <t>Status (2026-04-25): Design locked. Encode each shot's full per-frame PNG sequence (Node 9 output) into a single deliverable MP4 at 25 FPS. ffmpeg via imageio-ffmpeg static binary (same wheel Node 3 uses); codec = H.264 (libx264), pixel format = yuv420p, CRF = 18 (visually lossless on BnW line art), preset = medium. Output = &lt;work-dir&gt;/output/&lt;shotId&gt;_refined.mp4 (project-level dir for easy client hand-off). Post-encode ffprobe verifies codec/fps/nb_frames. Odd canvas dimensions are a hard error (libx264 requires even W/H; auto-padding would silently desync from Node 9 positions). Do NOT delete upstream artifacts (intermediates kept for debugging + Part 2 ToonCrafter reuse). CLI: run_node10.py --node9-result &lt;path&gt; [--crf 18] (only knob; everything else locked). Pipeline Option-C template (pipeline/node10.py + thin ComfyUI wrapper). Pure-Python subprocess + imageio_ffmpeg + json. No new deps.</t>
         </is>
       </c>
     </row>
@@ -2792,32 +2792,32 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>FFmpeg encoding</t>
+          <t>Load + validate inputs</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>PNG sequence to MP4.</t>
+          <t>Read node9_result.json (schemaVersion==1), chase pointers to per-shot timed_map.json, verify per-shot &lt;shot&gt;/timed/ directory exists with the expected frame_NNNN.png count.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>PNG sequence</t>
+          <t>node9_result.json (--node9-result); per-shot timed_map.json; per-shot timed/ directory</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Raw MP4</t>
+          <t>Validated in-memory shot list with timed-dir paths and expected frame counts</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>FFmpeg</t>
+          <t>Python stdlib (json, pathlib)</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Use high-quality codec (prores / h264 CRF low).</t>
+          <t>Raises Node9ResultInputError or TimedFramesError on structural problems. Locked decision #15 (single --node9-result CLI flag).</t>
         </is>
       </c>
     </row>
@@ -2830,30 +2830,34 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>25 FPS encoding</t>
+          <t>Probe canvas dimensions</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Match source rate.</t>
+          <t>Open one PNG per shot (frame_0001.png), read (W, H). If either is odd, raise FFmpegEncodeError with a clear 'libx264 requires even dimensions' message. Operator re-encodes source MP4 with even dimensions.</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>&lt;shot&gt;/timed/frame_0001.png (probe target)</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>25 FPS MP4</t>
+          <t>Per-shot (W, H) tuple; or FFmpegEncodeError on odd dims</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>FFmpeg</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="n"/>
+          <t>PIL.Image.open + .size</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Locked decision #11 (odd dims = hard error, NOT auto-pad). Auto-padding would shift every character by half a pixel and silently desync Node 9 positions.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="4" t="n"/>
@@ -2864,30 +2868,34 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Filename convention</t>
+          <t>ffmpeg encode</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>shot_XXX_refined.mp4.</t>
+          <t>ffmpeg -y -hide_banner -loglevel error -framerate 25 -i &lt;shot&gt;/timed/frame_%04d.png -c:v libx264 -pix_fmt yuv420p -crf &lt;crf&gt; -preset medium &lt;work&gt;/output/&lt;shotId&gt;_refined.mp4. Non-zero exit raises FFmpegEncodeError with last 10 stderr lines.</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>&lt;shot&gt;/timed/frame_*.png + canvas dims from 10B + CRF (default 18)</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Named output file</t>
+          <t>&lt;work-dir&gt;/output/&lt;shotId&gt;_refined.mp4 (H.264, yuv420p, 25 FPS)</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>FFmpeg output argument</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="n"/>
+          <t>imageio_ffmpeg static binary + subprocess</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Locked decisions #1 (imageio-ffmpeg, not system) + #2 (libx264) + #3 (yuv420p) + #4 (CRF 18) + #5 (preset medium) + #6 (25 FPS hardcoded) + #7 (output to &lt;work&gt;/output/) + #8 (filename pattern &lt;shotId&gt;_refined.mp4) + #17 (-y overwrite for rerun safety).</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="4" t="n"/>
@@ -2898,32 +2906,32 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Output validation</t>
+          <t>ffprobe verification</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Duration, frame count, codec checks.</t>
+          <t>ffprobe -v error -select_streams v:0 -show_entries stream=codec_name,r_frame_rate,nb_frames -of json &lt;output.mp4&gt;. Parse JSON; require codec_name==h264, r_frame_rate parses to 25.0 +/-0.01, nb_frames matches input PNG count within +/-1. Mismatch raises FFmpegEncodeError.</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Final MP4</t>
+          <t>&lt;output.mp4&gt; from 10C + expected PNG count from 10A</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Validation report</t>
+          <t>Pass/fail check; ffprobe parsed metadata for the aggregate manifest</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>ffprobe</t>
+          <t>imageio_ffmpeg + subprocess + json</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Hard check before marking shot done.</t>
+          <t>Locked decision #9 (catches silent ffmpeg corruption: exit 0 but malformed file). Cheap (~50ms per shot).</t>
         </is>
       </c>
     </row>
@@ -2936,32 +2944,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Archive working files</t>
+          <t>Emit aggregate manifest</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Keep PNG sequence + intermediates for debugging / Part 2 reuse.</t>
+          <t>Write &lt;work-dir&gt;/node10_result.json listing every shot's {shotId, outputPath, frameCount, durationSeconds, codec, fps, fileSizeBytes}. No per-shot manifest beyond this entry - Node 10's output is the deliverable itself, not a pointer.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Working folder</t>
+          <t>Verified outputs from 10D</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Archived /work/shot_XXX/</t>
+          <t>&lt;work-dir&gt;/node10_result.json</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Filesystem</t>
+          <t>Python json</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Part 2 (ToonCrafter) will need these.</t>
+          <t>Locked decision #10 (do NOT delete upstream artifacts - intermediates stay for debugging + Part 2 ToonCrafter reuse). Node 10 is purely additive.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Status (2026-04-25): Design locked. Encode each shot's full per-frame PNG sequence (Node 9 output) into a single deliverable MP4 at 25 FPS. ffmpeg via imageio-ffmpeg static binary (same wheel Node 3 uses); codec = H.264 (libx264), pixel format = yuv420p, CRF = 18 (visually lossless on BnW line art), preset = medium. Output = &lt;work-dir&gt;/output/&lt;shotId&gt;_refined.mp4 (project-level dir for easy client hand-off). Post-encode ffprobe verifies codec/fps/nb_frames. Odd canvas dimensions are a hard error (libx264 requires even W/H; auto-padding would silently desync from Node 9 positions). Do NOT delete upstream artifacts (intermediates kept for debugging + Part 2 ToonCrafter reuse). CLI: run_node10.py --node9-result &lt;path&gt; [--crf 18] (only knob; everything else locked). Pipeline Option-C template (pipeline/node10.py + thin ComfyUI wrapper). Pure-Python subprocess + imageio_ffmpeg + json. No new deps.</t>
+          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node10.py + pipeline/cli_node10.py + run_node10.py + custom_nodes/node_10_png_to_mp4/__init__.py + tests/test_node10.py (42 tests pass, 342 repo-wide). Pure-Python subprocess + imageio_ffmpeg + json. No GPU, no new deps. ffmpeg via imageio-ffmpeg static binary; codec H.264 (libx264) + yuv420p + medium preset + CRF 18 default + 25 FPS hardcoded. Output to &lt;work-dir&gt;/output/&lt;shotId&gt;_refined.mp4. Post-encode verification via imageio_ffmpeg.count_frames_and_secs (catches silent ffmpeg corruption: exit 0 but malformed file). Odd canvas dims fail-loud (libx264 requires even W/H; auto-padding would silently desync Node 9 positions). Does NOT delete upstream artifacts (intermediates kept for debugging + Part 2 ToonCrafter reuse). Rerun is atomic via ffmpeg -y flag. Multi-shot batches encode each into the same output/ directory.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Runs across all shots.</t>
+          <t>Status (2026-04-25): Design locked. Project-level orchestrator -- subprocess each run_nodeN.py in sequence and read its exit code. Single Node 11 invocation = one whole project end-to-end (Nodes 2-10). No batch-by-batch iteration (downstream nodes already process all shots in one pass). Default retries = 0 (fail-fast); per-node override via --retry-nodeN &lt;int&gt;. Pre-Node-7 best-effort nvidia-smi check. NO active VRAM monitoring in v1. Stdout passes through to operator + tee'd to &lt;work-dir&gt;/node11_progress.jsonl. Final report = &lt;work-dir&gt;/node11_result.json. Exit-code semantics differ from Nodes 2-10: partial success = exit 0 (with failedCount in JSON for CI), 100% failure = exit 1. NO resume in v1 (each node is rerun-safe so re-running just regenerates everything). Single-threaded. --dry-run passes through to Node 7. Pipeline Option-C template (pipeline/node11.py + thin ComfyUI wrapper). Pure-Python subprocess + json + datetime. No new deps.</t>
         </is>
       </c>
     </row>
@@ -3020,30 +3020,34 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Queue next shot</t>
+          <t>Pre-flight checks</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>After current shot completes, pull the next.</t>
+          <t>Verify --input-dir exists + readable; load metadata.json + characters.json minimally to confirm well-formed; if Node 7 will be live (not --dry-run), shell-out to nvidia-smi and log GPU info (warn but proceed if not available).</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Queue state</t>
+          <t>--input-dir &lt;path&gt;; --dry-run flag</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Active shot handoff</t>
+          <t>Validated input dir; logged GPU info (or warning); InputDirError on bad inputs</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="n"/>
+          <t>Python pathlib + json + subprocess (nvidia-smi best-effort)</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Locked decision #7 (best-effort GPU check, NOT a hard gate). Catches 'operator forgot to set up the pod' before Node 7 burns minutes.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="4" t="n"/>
@@ -3054,30 +3058,34 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Progress tracking &amp; logging</t>
+          <t>Sequential per-node execution</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Per-shot status, timing, errors.</t>
+          <t>For each node N in 2..10: build the appropriate run_nodeN.py argv with chained --node{N-1}-result paths, spawn subprocess with stdout/stderr passthrough + JSONL tee, time it, capture exit code. On non-zero exit: retry up to --retry-nodeN times (default 0). On final non-zero: record as failed.</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Pipeline events</t>
+          <t>Validated input from 11A + per-node retry overrides</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Log file / dashboard</t>
+          <t>All Node 2-10 outputs on disk + per-(shotId, nodeN, attempt) JSONL events</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Python logging</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="n"/>
+          <t>Python subprocess (no capture; passthrough) + json (tee to JSONL)</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Locked decisions #1 (subprocess, NOT in-process import), #5 (default retries=0), #6 (per-node retry override), #10 (real-time stdout passthrough + JSONL tee).</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="4" t="n"/>
@@ -3088,32 +3096,32 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Error handling &amp; retry</t>
+          <t>Per-shot status tracking</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Configurable retries per failed node.</t>
+          <t>Aggregate per-shot per-node status by reading downstream nodes' own per-shot manifests. A shot is 'succeeded' iff &lt;shotId&gt;_refined.mp4 exists in &lt;work-dir&gt;/output/ after Node 10; otherwise 'failed', with the failing node number recorded.</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Failure signals</t>
+          <t>Per-shot manifests from Nodes 2-10 + final output/ directory</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Retry or fail-forward decision</t>
+          <t>Per-shot status dict {shotId: {status, failingNode, nodeStatuses[], refinedMp4Path}}</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Python json + pathlib</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Cap retries to avoid infinite loops.</t>
+          <t>Locked decision #11 (final report aggregates by reading downstream manifests, not by mutating during 11B's run loop). Cleanly separates 'run the nodes' from 'compute the report'.</t>
         </is>
       </c>
     </row>
@@ -3126,32 +3134,32 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>RunPod GPU / VRAM monitoring</t>
+          <t>Final report</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Pause or reduce batch if OOM risk.</t>
+          <t>Write &lt;work-dir&gt;/node11_result.json with per-shot per-node status + timing + final-MP4 path + total batch wall time. Stdout summary: [node11] OK - N shots / M succeeded / K failed, total Xs, MP4s in &lt;output_dir&gt;/.</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>nvidia-smi telemetry</t>
+          <t>Per-shot status from 11C + per-node timings from 11B</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Dynamic batch adjustment</t>
+          <t>&lt;work-dir&gt;/node11_result.json + stdout summary line</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>nvidia-smi / pynvml</t>
+          <t>Python json + datetime</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Protect against OOM crashes.</t>
+          <t>Locked decisions #11 (single consumable JSON artifact) + #12 (consistent CLI summary shape with other 9 nodes). NO active VRAM monitoring (#8) -- documented as known limitation.</t>
         </is>
       </c>
     </row>
@@ -3164,32 +3172,32 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Final batch report</t>
+          <t>Exit-code resolution</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Summary of successes, failures, per-shot runtime.</t>
+          <t>Exit 0 if at least one shot succeeded (partial success counts as 0); exit 1 if all failed (BatchAllFailedError) or on Node11Error subclass (InputDirError, NodeStepError); exit 2 on unexpected exception.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Logs</t>
+          <t>Per-shot status from 11C</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>batch_report.json / html</t>
+          <t>Process exit code 0 / 1 / 2</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Python sys.exit</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Delivered alongside refined MP4s.</t>
+          <t>Locked decision #13 (Node 11 owns the partial-success semantic; individual nodes can't because they fail the whole batch by design). Differs from Nodes 2-10's exit-code policy intentionally.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Status (2026-04-25): Design locked. Project-level orchestrator -- subprocess each run_nodeN.py in sequence and read its exit code. Single Node 11 invocation = one whole project end-to-end (Nodes 2-10). No batch-by-batch iteration (downstream nodes already process all shots in one pass). Default retries = 0 (fail-fast); per-node override via --retry-nodeN &lt;int&gt;. Pre-Node-7 best-effort nvidia-smi check. NO active VRAM monitoring in v1. Stdout passes through to operator + tee'd to &lt;work-dir&gt;/node11_progress.jsonl. Final report = &lt;work-dir&gt;/node11_result.json. Exit-code semantics differ from Nodes 2-10: partial success = exit 0 (with failedCount in JSON for CI), 100% failure = exit 1. NO resume in v1 (each node is rerun-safe so re-running just regenerates everything). Single-threaded. --dry-run passes through to Node 7. Pipeline Option-C template (pipeline/node11.py + thin ComfyUI wrapper). Pure-Python subprocess + json + datetime. No new deps.</t>
+          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node11.py + pipeline/cli_node11.py + run_node11.py + custom_nodes/node_11_batch_manager/__init__.py + tests/test_node11.py (46 tests pass, 388 repo-wide). Pure-Python orchestrator subprocess + json + datetime. No GPU, no new deps. Subprocess-invokes run_nodeN.py for N in 2..10 in sequence; per-node retry via --retry-nodeN &lt;int&gt; (default 0); pre-Node-7 best-effort nvidia-smi (warn-and-proceed); JSONL progress log + final aggregate report; partial-success semantic = exit 0 with failedShots in JSON; 100% failure = BatchAllFailedError exit 1; --dry-run propagates to Node 7. With Node 11 shipped, the entire 11-node pipeline is end-to-end complete.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node11.py + pipeline/cli_node11.py + run_node11.py + custom_nodes/node_11_batch_manager/__init__.py + tests/test_node11.py (46 tests pass, 388 repo-wide). Pure-Python orchestrator subprocess + json + datetime. No GPU, no new deps. Subprocess-invokes run_nodeN.py for N in 2..10 in sequence; per-node retry via --retry-nodeN &lt;int&gt; (default 0); pre-Node-7 best-effort nvidia-smi (warn-and-proceed); JSONL progress log + final aggregate report; partial-success semantic = exit 0 with failedShots in JSON; 100% failure = BatchAllFailedError exit 1; --dry-run propagates to Node 7. With Node 11 shipped, the entire 11-node pipeline is end-to-end complete.</t>
+          <t>Status (2026-04-25): DONE - design-locked + shipped same day. pipeline/node11.py + pipeline/cli_node11.py + run_node11.py + custom_nodes/node_11_batch_manager/__init__.py + tests/test_node11.py (46 tests pass, 388 repo-wide). Pure-Python orchestrator subprocess + json + datetime. No GPU, no new deps. Subprocess-invokes run_nodeN.py for N in 2..10 in sequence; per-node retry via --retry-nodeN &lt;int&gt; (default 0); pre-Node-7 best-effort nvidia-smi (warn-and-proceed); JSONL progress log + final aggregate report; partial-success semantic = exit 0 with failedShots in JSON; 100% failure = BatchAllFailedError exit 1; --dry-run propagates to Node 7. With Node 11 shipped, the entire 11-node pipeline is end-to-end complete. Live RunPod verification (2026-04-25, RTX 4090): 1 shot succeeded / 0 failed in 33.8s end-to-end via single run_node11.py call. Per-node: Nodes 2-6 + 8-10 each &lt;1s; Node 7 LIVE SD generation (lineart-fallback) dominated at 30.4s; orchestration overhead ~2s. Pre-Node-7 nvidia-smi check fired correctly. Bringup gap caught: system python3 needs pipeline/requirements.txt installed (the runpod-slim venv has Comfy's deps but the system Python doesn't until pip install -r requirements.txt). Captured in tools/POD_NOTES_runpod_slim.md (new step 5).</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,6 +124,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -523,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7.77734375" customWidth="1" min="1" max="1"/>
@@ -2053,11 +2056,11 @@
           <t>ComfyUI workflow JSON + thin custom-node wrapper (breaks pipeline/node*.py template on purpose); SD 1.5 + AnyLoRA line-art checkpoint + optional BnW LoRA; DWPose preprocessor + DWPose CN; LineArt + Scribble CN (non-human fallback); IP-Adapter-Plus; RunPod-only</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Locked 2026-04-23: separate pose (from rough skeleton) from identity (from Node 6 reference crop); per-character poseExtractor routing via characters.json (dwpose default for humans, lineart-fallback for non-humans like Jaggu); IP-Adapter fed the COLOR reference crop; txt2img (not img2img) so rough pixels do not bleed; per-character generation then Node 8 composites; SD 1.5 + AnyLoRA + optional BnW LoRA; DPM++ 2M Karras 25 steps CFG 7.0 512x512; seed logged per (shotId, keyPoseIndex, identity); RunPod-only (no local VRAM for full stack); ComfyUI-Manager for dev convenience + curl+SHA pins in runpod_setup.sh + models.json for production; no QC v1 -- metadata logging only, retry is a future Node 11C hook; transparent-background PNG output. Runtime topology: ComfyUI runs on the RunPod pod, not the laptop; laptop produces Nodes 2-6 outputs via CPU-only CLIs and syncs the work-dir to the pod; on the pod runpod_setup.sh symlinks custom_nodes/node_07_pose_refiner into ComfyUI and curl-downloads models.json pins; `python run_node7.py` runs on the pod and POSTs workflow.json to ComfyUI's HTTP API; local ComfyUI_windows_portable is for Nodes 3-6 wrapper authoring/smoke-tests only (insufficient VRAM for Node 7's SD 1.5 + ControlNet + IP-Adapter + DWPose stack). Status (2026-04-24): DONE -- scaffold shipped. 47 tests pass (207 repo-wide). Files: pipeline/cli_node7.py + run_node7.py + custom_nodes/node_07_pose_refiner/{__init__.py, manifest.py, comfyui_client.py, orchestrate.py, workflow.json, workflow_lineart_fallback.json, models.json, README.md} + runpod_setup.sh (extended with custom-node clone + curl weight download + sha256 verify) + tests/test_node7.py. Typed errors: Node7Error base + Node6ResultInputError + RefinementGenerationError + WorkflowTemplateError + ComfyUIError (QueueLookupError reused from Node 5). CLI exit 0 success (per-generation errors still exit 0), 1 (Node7Error, QueueLookupError) whole-run failure, 2 unexpected. Live RunPod run pending first execution (ComfyUI contact + real weights).
 Status (2026-04-25): DONE - both routes live-verified on RunPod. First live run (lineart-fallback both characters): 2 generated / 0 skipped / 0 error, 36s wall time, 2-character synthetic smoke fixture. DWPose verification (same fixture, Bhim flipped to dwpose, Jaggu still lineart-fallback): 2 generated / 0 skipped / 0 error, 41s wall time, both routes in the same Node 7 invocation; per-character routing table works; Bhim PNG bytes differ from baseline (sha d77d9b18.. vs 038f69e6..) confirming DWPose contributes pose info; Jaggu PNG bytes are bit-identical (sha 5aa3c619..) confirming the deterministic-seed contract holds for unchanged routes. Runpod-slim pod image needed FOUR bringup steps (symlink comfyui_controlnet_aux, write extra_model_paths.yaml, add weight_type: standard to both workflow JSONs, pip-install matplotlib + scikit-image + onnxruntime into the venv for DWPose) - all captured in tools/POD_NOTES_runpod_slim.md and the Node 7 - live-run addendum of CLAUDE.md.
-</t>
+Phase 2 (Flux migration) — design-locked 2026-04-26, code not yet shipped. Real-shot TMKOC test (EP35 SH004) succeeded mechanically end-to-end in 33.8s on the 4090 but produced anime-girl output instead of TMKOC characters because SD 1.5 + AnyLoRA is anime-trained. Hug-test proof-of-concept (Flux Dev fp8 + Flat Cartoon Style v1.2 + ControlNet Union Pro + DWPose + txt2img, single generation, no IP-Adapter) on the same pod generated dramatically better output (~70s on the 4090) — recognizable Tappu + Champak Lal in TMKOC style. 14 architectural decisions locked across CLAUDE.md 'Node 7 v2 — locked decisions' + PLAN.md 'NODE 7 v2': (1) Flux Kontext Dev fp16 base; (2) Flat Cartoon Style v1.2 LoRA @ 0.75, replaced by custom-trained TMKOC v1 in Phase 2d; (3) ControlNet Union Pro (single CN, routes via SetUnionControlNetType) @ 0.65; (4) XLabs Flux IP-Adapter v2 @ 0.8 (requires x-flux-comfyui custom node); (5) img2img with denoise=0.55 (REVERSES Phase 1 txt2img — Flux Kontext Dev's superior denoising resolves the rough-pixel-bleed concern); (6) CN 0.65 + IP-Adapter 0.8; (7) 1280x720 native (matches source MP4); (8) dpmpp_2m_sde + simple + 40 steps + FluxGuidance 4.0 + CFG 1.0; (9) per-character LoRAs Phase 2e — plan architecture, defer training, bootstrap data via Phase 2b IP-Adapter, ai-toolkit (ostris) on A100 80GB ~$5-15 + 1.5h per character; (10) backward-compat: schemaVersion stays 1, all changes additive; (11) A100 80GB + Flux Dev fp16 default, fp8 fallback via --precision flag; (12) Phase 1 weights archived (deprecated:true, removal scheduled 2026-10-26); (13) architecture template unchanged (workflow JSON + thin custom-node wrapper, no pipeline/node7.py); (14) failure mode unchanged (log + continue, no QC gate in v1; future Node 11C retry hook is the right home for operator-level retries). Implementation roadmap rows 71-77 (sub-steps 7v2-A through 7v2-G). Hug-test workflow JSON at _pod_out/flux_tmkoc_test_workflow.json is the implementation starting point for workflow_flux_v2.json.</t>
         </is>
       </c>
     </row>
@@ -3202,14 +3205,270 @@
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>7v2-A</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Phase 2a — Flux + Style LoRA + Union CN integration</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Replace Phase 1's SD 1.5 + AnyLoRA workflow with a Flux Dev fp16 + Flat Cartoon Style v1.2 LoRA + ControlNet Union Pro stack. txt2img mode for first ship (img2img comes in Phase 2c). Add precision-fallback for smaller GPUs. Default still v1 for safety; v2 callable via --workflow flag.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Existing Phase 1 inputs (node6_result.json + queue.json) + new Flux + LoRA + Union CN weights downloaded by runpod_setup.sh per models.json pins.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>New custom_nodes/node_07_pose_refiner/workflow_flux_v2.json (16 locked node IDs); modified models.json (Phase 2 weights added; Phase 1 weights flipped to deprecated:true with scheduled removal 2026-10-26); modified runpod_setup.sh (Phase 2 weight downloads + DOWNLOAD_DEPRECATED env var handling); modified pipeline/cli_node7.py (new --workflow {v1,v2} default v1 + --precision {fp16,fp8} default fp16 flags); modified custom_nodes/node_07_pose_refiner/orchestrate.py (routing + Flux variable substitution); test_node7.py Phase 2 cases.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Flux Dev fp16/fp8 (BFL); T5-XXL fp16/fp8; CLIP-L; Flux VAE (ae.safetensors); Flat Cartoon Style v1.2 (Civitai 644541 v 740091); ControlNet Union Pro (Shakker-Labs); ai-toolkit not yet (Phase 2d).</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Hug-test proof-of-concept at _pod_out/flux_tmkoc_test_workflow.json is the implementation starting point for workflow_flux_v2.json. Per-node ship checklist applies (CLAUDE.md ship checklist section). Phase 2 schema additions (per #10 backward-compat): models.json gains deprecated/deprecatedSince/deprecatedReason/scheduledRemovalDate/precision fields (all optional with defaults). RefinedGeneration manifest gains workflowName/precision/characterLoraFilename fields (optional, default 'v1'/'fp8'/None for Phase 1 round-trip). CLI flags pass through Node 11 unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>7v2-B</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2b — Add XLabs Flux IP-Adapter</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Add identity-injection layer to Phase 2a's workflow via the XLabs-AI Flux IP-Adapter v2 (~1 GB weight). Wires character reference crop into the Flux stack so generated character matches the model sheet across multiple key poses. Reuses Node 6's color reference crops (no Node 6 changes here).</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2a workflow + Node 6's color reference crops (existing).</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Modified runpod_setup.sh (clones x-flux-comfyui custom node from XLabs-AI; downloads flux-ip-adapter-v2.safetensors); modified workflow_flux_v2.json (IP-Adapter nodes wired in); identity-preservation regression test on the TMKOC fixture (same character across multiple key poses must have consistent face / outfit).</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>XLabs-AI x-flux-comfyui custom node; flux-ip-adapter-v2.safetensors weight; T5-XXL + CLIP-L (already loaded by Phase 2a's DualCLIPLoader).</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>7v2-C</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2c — Switch Node 7 default to v2 (img2img mode, denoise=0.55)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Flip --workflow default from v1 to v2; switch workflow_flux_v2.json from txt2img to img2img mode. Rough crop is VAEEncoded into the latent and KSampler runs at denoise=0.55 — preserves rough composition (positions, scale, silhouette) while regenerating line quality + character identity. Phase 1 path stays callable via --workflow=v1 throughout the 6-month deprecation window.</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2b workflow + Node 5/6/7 inputs unchanged.</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Modified workflow_flux_v2.json (LoadImage node 50 + VAEEncode node 80 wired in place of EmptySD3LatentImage; KSampler node 90's denoise param set to 0.55); modified pipeline/cli_node7.py (--workflow default flips to v2); end-to-end real-shot validation against TMKOC fixture (5+ shots).</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Same as Phase 2b stack; no new weights or custom nodes.</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Locked decision #5 reverses Phase 1's txt2img — Flux Kontext Dev's superior denoising resolves the original 'rough pixels would bleed into output' concern. denoise=0.55 is the locked default; tuning per-shot is a future operator concern. After Phase 2c lands, Phase 2 is the production path; v1 stays as rollback insurance only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>7v2-D</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2d — Train TMKOC style LoRA</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Replace generic Flat Cartoon Style v1.2 with a custom-trained TMKOC v1 style LoRA. Higher per-shot fidelity to the actual Indian children's animation aesthetic (vs. generic flat-cartoon). Optional but recommended for client-deliverable quality.</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Training data: curated TMKOC frame extracts OR Phase 2c img2img output from prior client batches OR commissioned artist references. ~50-100 high-quality training images.</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Trained LoRA weight tmkoc_style_v1.safetensors; modified models.json (new LoRA pinned with sha256); modified workflow_flux_v2.json (LoraLoader node 20's lora_name swapped from flat_cartoon_style_v12 to tmkoc_style_v1).</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>ai-toolkit (ostris) on A100 80GB; ~1.5h training + ~$5 RunPod time. CogVLM or GPT-4V for image captioning before training.</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Caption discipline matters: caption everything that ISN'T the TMKOC style (subject, pose, expression, background) so the LoRA learns 'TMKOC style' as the residual rather than memorizing specific scenes. Strength tuning per-LoRA (start at 0.75, adjust 0.6-0.9 based on test runs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>7v2-E</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2e — Train per-character LoRAs (one commit per character)</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Optional max-quality identity injection: stack a character-specific LoRA (e.g. TAPPU_v1.safetensors, CHAMPAK_LAL_v1.safetensors) on top of the TMKOC style LoRA. Pushes identity quality from ~85% (IP-Adapter alone) to ~95%. Per-character LoRAs are loaded via a chained LoraLoader (node 21) selected per-detection from characters.json.characterLoraFilename.</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Per character: 50-100 training images bootstrapped from the model sheet via Phase 2b's IP-Adapter (generate variations, curate best 60-80, caption with CogVLM/GPT-4V).</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Per character: trained &lt;NAME&gt;_v1.safetensors; modified models.json (new LoRA pinned); modified characters.json (characterLoraFilename + characterLoraStrength fields populated for the character — additive schema per #10 means old characters.json files still load with these fields null/0.85). Per-character ComfyUI test (10+ generations across varied poses) verifies consistent identity.</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Same ai-toolkit + A100 80GB stack as Phase 2d; ~1.5h + ~$5-15 per character.</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Order matters per Phase 2 locked decision #9: train per-character LoRAs ONLY after Phase 2d's TMKOC style LoRA ships — character LoRAs trained against the wrong base style would need re-training when style changes. Strength stacking: style LoRA at 0.75 + character LoRA at 0.85 (tune per character; over-stacking causes the two LoRAs to fight). One ship-checklist commit per character, mirroring per-node discipline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>7v2-F</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2f — Fix Node 5 background-line detection bug (upstream prerequisite)</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>Real TMKOC test exposed a Node 5 failure mode: when the rough animatic has sketched background lines (panels, furniture, scene boundaries), Otsu binarization picks them up as one giant connected component covering the entire frame — a single character bbox of [0, 0, 1280, 720] for the whole key pose. Cascades into garbage Node 6 angle picks (essentially random) → wrong character generated by Node 7. Doesn't touch Node 7 directly but is an upstream prerequisite for clean Phase 2c output on real client shots.</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Existing Node 5 inputs (node4_result.json + queue.json).</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Modified pipeline/node5.py: Otsu fallback when bbox spans &gt;70% of frame (re-runs detection with a stricter threshold; if still oversized, splits via metadata-driven region-of-interest hints). Modified frontend/index.html to optionally capture per-shot bbox hints. Test fixture for the TMKOC background-line failure mode.</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>scipy + Pillow (existing Node 5 stack); no new deps.</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Out of strict Node 7 scope but blocking real Phase 2c quality verification. Schedule: ship before or alongside Phase 2c so Phase 2c's first real client validation isn't sabotaged by Node 5 garbage upstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>7v2-G</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2g — Simplify Node 6 (always pick 'front' angle when IP-Adapter handles identity)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>When Phase 2b+ IP-Adapter handles identity correction regardless of which reference angle was passed in, Node 6's per-key-pose 8-way angle classification becomes redundant overhead. Make Node 6's angle picking optional: --angle-strategy {classical,front-only} flag, default front-only when Phase 2b is active, classical otherwise. Saves ~ms per key pose; more importantly removes a class of low-confidence angle picks that produced cascading garbage in the real-shot test.</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Existing Node 6 inputs (node5_result.json + queue.json + characters.json).</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Modified pipeline/node6.py (front-only mode that always picks the 'front' angle from the sliced reference sheet for every detection); modified pipeline/cli_node6.py (--angle-strategy flag); test cases for both modes.</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Existing Node 6 stack (numpy + scipy + Pillow); no new deps.</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Optional simplification — Node 6's classical multi-signal angle picker still works and can stay the default. front-only mode is a Phase 2b+ optimization since the IP-Adapter does the identity heavy-lifting from a single reference angle just as well as from the 'best' angle.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3238,7 +3238,8 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Hug-test proof-of-concept at _pod_out/flux_tmkoc_test_workflow.json is the implementation starting point for workflow_flux_v2.json. Per-node ship checklist applies (CLAUDE.md ship checklist section). Phase 2 schema additions (per #10 backward-compat): models.json gains deprecated/deprecatedSince/deprecatedReason/scheduledRemovalDate/precision fields (all optional with defaults). RefinedGeneration manifest gains workflowName/precision/characterLoraFilename fields (optional, default 'v1'/'fp8'/None for Phase 1 round-trip). CLI flags pass through Node 11 unchanged.</t>
+          <t>Hug-test proof-of-concept at _pod_out/flux_tmkoc_test_workflow.json is the implementation starting point for workflow_flux_v2.json. Per-node ship checklist applies (CLAUDE.md ship checklist section). Phase 2 schema additions (per #10 backward-compat): models.json gains deprecated/deprecatedSince/deprecatedReason/scheduledRemovalDate/precision fields (all optional with defaults). RefinedGeneration manifest gains workflowName/precision/characterLoraFilename fields (optional, default 'v1'/'fp8'/None for Phase 1 round-trip). CLI flags pass through Node 11 unchanged.
+Status (2026-04-26): SHIPPED — same day as design-lock, mirroring the Nodes 8-11 pattern (design-lock + ship same day). 84 Node 7 tests pass (47 Phase 1 + 37 new Phase 2; 429 repo-wide, zero regressions on every prior Node 2-11 test). Files shipped: custom_nodes/node_07_pose_refiner/workflow_flux_v2.json (16 locked Phase 2 node IDs); modified custom_nodes/node_07_pose_refiner/{orchestrate.py, manifest.py, models.json, __init__.py, README.md} + pipeline/{cli_node7.py, cli_node11.py, node11.py, node2.py, schemas.py} + runpod_setup.sh + tests/{test_node7.py, test_node11.py, test_node2.py}. Default --workflow=v1 means existing pipelines keep working unchanged; v2 is opt-in via the new flag until Phase 2c lands. Phase 1 weights flipped to deprecated:true with 2026-10-26 removal date; runpod_setup.sh skips them by default (DOWNLOAD_DEPRECATED=true opts back in for rollback). Phase 2b is the next ship-checklist step — XLabs Flux IP-Adapter v2 via x-flux-comfyui custom node clone.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3277,7 +3277,8 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).</t>
+          <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).
+Status (2026-04-27): SHIPPED. 91 Node 7 tests pass (47 Phase 1 + 44 Phase 2; 436 repo-wide, zero regressions). Wired XLabs Flux IP-Adapter v2 into workflow_flux_v2.json via 3 additive locked node IDs: 22 ('Load Flux IPAdatpter' [sic - upstream typo preserved verbatim because that's the registered class_type], 23 (LoadImage for the reference COLOR crop from Node 6E), 24 ('Apply Flux IPAdapter'). Only existing-node change is KSampler's model input rewiring from node 20 (style LoRA output) to node 24 (IP-Adapter wrapped model). ip_scale=0.8 per locked decision #6 (XLabs default is 0.93; we trade a bit of identity strength for slightly looser pose adherence -- better for varied keyposes across a shot). Reference image is the COLOR crop, NOT the DoG line-art crop, per locked decision #4. models.json gained 2 new weight pins: flux-ip-adapter-v2.safetensors (~1 GB at models/ipadapter-flux/) and clip-vit-large-patch14.safetensors (~600 MB at models/clip_vision/ for the IP-Adapter's vision encoder; distinct from the Phase 2a clip_l text encoder). models.json customNodes also gained the x-flux-comfyui clone from XLabs-AI. orchestrate.py gained NODE_FLUX_IPADAPTER_LOADER/_REF_IMAGE/_APPLY constants + parameterizer wires task.referenceColorCropPath into node 23 + re-asserts ip_scale = V2_STRENGTH_IP_ADAPTER. 7 new tests cover the shipped-JSON regression (IP-Adapter nodes present + correct class_type strings with typos + KSampler rewired to node 24 + IP-Adapter Apply inputs wired correctly), parameterizer behaviour (reference color -&gt; node 23, ip_scale -&gt; V2_STRENGTH_IP_ADAPTER, rough-vs-reference path-swap guard), and fail-loud regression (missing IP-Adapter node raises WorkflowTemplateError). Phase 2c is the next ship-checklist step -- switch workflow_flux_v2.json from txt2img to img2img + flip --workflow default from v1 to v2.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3316,7 +3316,8 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>Locked decision #5 reverses Phase 1's txt2img — Flux Kontext Dev's superior denoising resolves the original 'rough pixels would bleed into output' concern. denoise=0.55 is the locked default; tuning per-shot is a future operator concern. After Phase 2c lands, Phase 2 is the production path; v1 stays as rollback insurance only.</t>
+          <t>Locked decision #5 reverses Phase 1's txt2img — Flux Kontext Dev's superior denoising resolves the original 'rough pixels would bleed into output' concern. denoise=0.55 is the locked default; tuning per-shot is a future operator concern. After Phase 2c lands, Phase 2 is the production path; v1 stays as rollback insurance only.
+Status (2026-04-27): SHIPPED. 96 Node 7 tests pass (47 Phase 1 + 49 Phase 2; 441 repo-wide, zero regressions). TWO architecturally significant flips: (1) workflow_flux_v2.json node 80 swapped from EmptySD3LatentImage(1280, 720) [txt2img] to VAEEncode(pixels=node-50, vae=node-12) [img2img] -- the rough crop now feeds into the latent via Flux's VAE; KSampler denoise dropped from 1.0 to 0.55 per locked decision #5. Flux Kontext Dev's superior denoising resolves Phase 1's 'rough pixels would bleed into output' concern -- at 0.55 the messy pencil scribbles vanish but the underlying composition (positions, scale, silhouette) stays. Output dimensions match the rough's native dims (Node 4 wrote them at source MP4 resolution); Node 8's compositor places refined PNGs at bbox positions per Node 8's locked decision #1, so exact output dims don't matter. (2) DEFAULT_WORKFLOW flipped from 'v1' to 'v2' in orchestrate.py -- v2 is now the production default; Phase 1 stays callable via --workflow=v1 for the entire 6-month deprecation window per locked decision #12 (until 2026-10-26). V2_DENOISE = 0.55 constant added; v2 parameterizer re-asserts it on every generation so a hand-edited JSON can't silently revert to txt2img's denoise=1.0. CLI success line for v2 reports 'precision=&lt;value&gt;' alongside 'workflow=v2' (was hidden under v1). 5 new tests cover img2img wiring (node 80 = VAEEncode with pixels from 50 + vae from 12 in shipped JSON), denoise lock (KSampler.denoise = 0.55 in shipped JSON + parameterizer re-asserts it), v2-as-default (DEFAULT_WORKFLOW + cfg.workflow + CLI success line all expect v2), and v1-still-callable-via-flag. 3 existing tests updated to pass workflow='v1' explicitly where they meant Phase 1 specifically (test_cn_strengths_for_dwpose, test_cn_strengths_for_lineart_fallback, test_cn_strengths_for_v1_explicit_returns_v1_split). Phase 2d is the next ship-checklist step -- replace generic Flat Cartoon Style v1.2 with a custom-trained TMKOC v1 style LoRA bootstrapped from Phase 2c's img2img output.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3355,7 +3355,8 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>Caption discipline matters: caption everything that ISN'T the TMKOC style (subject, pose, expression, background) so the LoRA learns 'TMKOC style' as the residual rather than memorizing specific scenes. Strength tuning per-LoRA (start at 0.75, adjust 0.6-0.9 based on test runs).</t>
+          <t>Caption discipline matters: caption everything that ISN'T the TMKOC style (subject, pose, expression, background) so the LoRA learns 'TMKOC style' as the residual rather than memorizing specific scenes. Strength tuning per-LoRA (start at 0.75, adjust 0.6-0.9 based on test runs).
+Status (2026-04-27): Phase 2d-prep SHIPPED; Phase 2d-run pending. 104 Node 7 tests pass (47 Phase 1 + 57 Phase 2; 449 repo-wide, zero regressions). Shipped the integration infrastructure for the TMKOC v1 style LoRA without yet training the actual safetensors weight (Phase 2d-run is a separate live-pod follow-up). Code: new --style-lora {flat_cartoon_v12,tmkoc_v1} flag (default flat_cartoon_v12) on pipeline/cli_node7.py + pipeline/cli_node11.py + ComfyUI wrapper style_lora dropdown -- parameterizes workflow_flux_v2.json node 20's lora_name based on the choice. STYLE_LORA_FILENAMES table + STYLE_LORA_CHOICES + DEFAULT_STYLE_LORA constants in orchestrate.py; OrchestrateConfig.__post_init__ validates the field. tmkoc-style-v1 placeholder entry added to models.json with url='TODO...' so runpod_setup.sh skips it gracefully until a real weight URL+sha256 ships -- destination models/loras/tmkoc_style_v1.safetensors, sizeMB ~80, role describes the contract. New files: tools/phase2d/PHASE2D_TRAINING_PLAYBOOK.md (full Path A bootstrap -&gt; curate -&gt; caption -&gt; train -&gt; validate -&gt; ship runbook; 6-step procedure with cost/time estimates: ~$10-15 GPU + ~12-18 hours human time per LoRA across 2-3 iterations) and tools/phase2d/ai_toolkit_config_template.yaml (locked Flux LoRA training params: rank=16, LR=1e-4, 2000 steps, batch_size=1, quantize=true, sample_every=250 -- operator copies it to a per-run name and fills 3 TODO fields before launching ai-toolkit). 8 new tests cover the flag plumbing (CLI accepts/rejects + default flat_cartoon_v12 + tmkoc_v1 swap), parameterizer wiring (node 20 lora_name flips per choice), config validation (invalid choice raises ValueError), and the contract between STYLE_LORA_FILENAMES and models.json destinations. Phase 2d-run is the next ship-checklist step -- actually train the TMKOC v1 LoRA on a live A100 pod by following the playbook, then a follow-up commit fills in models.json's tmkoc-style-v1 URL + sha256 from the trained safetensors weight.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3278,7 +3278,8 @@
       <c r="H72" s="9" t="inlineStr">
         <is>
           <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).
-Status (2026-04-27): SHIPPED. 91 Node 7 tests pass (47 Phase 1 + 44 Phase 2; 436 repo-wide, zero regressions). Wired XLabs Flux IP-Adapter v2 into workflow_flux_v2.json via 3 additive locked node IDs: 22 ('Load Flux IPAdatpter' [sic - upstream typo preserved verbatim because that's the registered class_type], 23 (LoadImage for the reference COLOR crop from Node 6E), 24 ('Apply Flux IPAdapter'). Only existing-node change is KSampler's model input rewiring from node 20 (style LoRA output) to node 24 (IP-Adapter wrapped model). ip_scale=0.8 per locked decision #6 (XLabs default is 0.93; we trade a bit of identity strength for slightly looser pose adherence -- better for varied keyposes across a shot). Reference image is the COLOR crop, NOT the DoG line-art crop, per locked decision #4. models.json gained 2 new weight pins: flux-ip-adapter-v2.safetensors (~1 GB at models/ipadapter-flux/) and clip-vit-large-patch14.safetensors (~600 MB at models/clip_vision/ for the IP-Adapter's vision encoder; distinct from the Phase 2a clip_l text encoder). models.json customNodes also gained the x-flux-comfyui clone from XLabs-AI. orchestrate.py gained NODE_FLUX_IPADAPTER_LOADER/_REF_IMAGE/_APPLY constants + parameterizer wires task.referenceColorCropPath into node 23 + re-asserts ip_scale = V2_STRENGTH_IP_ADAPTER. 7 new tests cover the shipped-JSON regression (IP-Adapter nodes present + correct class_type strings with typos + KSampler rewired to node 24 + IP-Adapter Apply inputs wired correctly), parameterizer behaviour (reference color -&gt; node 23, ip_scale -&gt; V2_STRENGTH_IP_ADAPTER, rough-vs-reference path-swap guard), and fail-loud regression (missing IP-Adapter node raises WorkflowTemplateError). Phase 2c is the next ship-checklist step -- switch workflow_flux_v2.json from txt2img to img2img + flip --workflow default from v1 to v2.</t>
+Status (2026-04-27): SHIPPED. 91 Node 7 tests pass (47 Phase 1 + 44 Phase 2; 436 repo-wide, zero regressions). Wired XLabs Flux IP-Adapter v2 into workflow_flux_v2.json via 3 additive locked node IDs: 22 ('Load Flux IPAdatpter' [sic - upstream typo preserved verbatim because that's the registered class_type], 23 (LoadImage for the reference COLOR crop from Node 6E), 24 ('Apply Flux IPAdapter'). Only existing-node change is KSampler's model input rewiring from node 20 (style LoRA output) to node 24 (IP-Adapter wrapped model). ip_scale=0.8 per locked decision #6 (XLabs default is 0.93; we trade a bit of identity strength for slightly looser pose adherence -- better for varied keyposes across a shot). Reference image is the COLOR crop, NOT the DoG line-art crop, per locked decision #4. models.json gained 2 new weight pins: flux-ip-adapter-v2.safetensors (~1 GB at models/ipadapter-flux/) and clip-vit-large-patch14.safetensors (~600 MB at models/clip_vision/ for the IP-Adapter's vision encoder; distinct from the Phase 2a clip_l text encoder). models.json customNodes also gained the x-flux-comfyui clone from XLabs-AI. orchestrate.py gained NODE_FLUX_IPADAPTER_LOADER/_REF_IMAGE/_APPLY constants + parameterizer wires task.referenceColorCropPath into node 23 + re-asserts ip_scale = V2_STRENGTH_IP_ADAPTER. 7 new tests cover the shipped-JSON regression (IP-Adapter nodes present + correct class_type strings with typos + KSampler rewired to node 24 + IP-Adapter Apply inputs wired correctly), parameterizer behaviour (reference color -&gt; node 23, ip_scale -&gt; V2_STRENGTH_IP_ADAPTER, rough-vs-reference path-swap guard), and fail-loud regression (missing IP-Adapter node raises WorkflowTemplateError). Phase 2c is the next ship-checklist step -- switch workflow_flux_v2.json from txt2img to img2img + flip --workflow default from v1 to v2.
+Phase 2d-fixup (2026-04-27, post-live-pod-debug): Live-pod verification on a fresh A100 80GB caught two real bugs in Phase 2b's ship that would have blocked Phase 2d-run / Phase 2e-run when actually invoking ComfyUI's HTTP API. (1) workflow_flux_v2.json had class_type 'Load Flux IPAdatpter' and 'Apply Flux IPAdapter' on nodes 22 + 24. ComfyUI's /object_info reported those classes NOT registered — but 'LoadFluxIPAdapter' and 'ApplyFluxIPAdapter' (no spaces, no typo) WERE registered. Phase 2b's agent research confused upstream's NODE_CLASS_MAPPINGS keys (the internal class names ComfyUI's wire format uses) with NODE_DISPLAY_NAME_MAPPINGS values (the GUI menu labels, where the 'IPAdatpter' typo lives). Workflow JSON's class_type field uses the keys, not the values. (2) models.json IP-Adapter destination 'models/ipadapter-flux/' was wrong — x-flux-comfyui's folder_paths.folder_names_and_paths['xlabs_ipadapters'] registration scans 'models/xlabs/ipadapters/' (os.path.join(models_dir, 'xlabs', 'ipadapters')). Files in the wrong dir never appear in LoadFluxIPAdapter's ipadatper field. Phase 2d-fixup corrects: workflow_flux_v2.json class_type strings + file-level _comment; models.json destination + both role descriptions; orchestrate.py NODE_FLUX_IPADAPTER_LOADER comment + _require_node human-name strings; tests/test_node7.py pinned strings (test_shipped_workflow_flux_v2_ipadapter_class_types) + _minimal_v2_template placeholder + test_v2_parameterize_missing_ipadapter_node_raises regex match; custom_nodes/node_07_pose_refiner/README.md Phase 2b row + 17-row workflow node ID table + footer note explaining wire-protocol class_type vs GUI display name distinction. The 'ipadatper' input FIELD name (typo'd) IS real and stays as-is — that's how XLabs registered the field name in LoadFluxIPAdapter.INPUT_TYPES. 449 tests pass after the fix; zero regressions. Pod was terminated to save budget; Phase 2d-run (actual TMKOC LoRA training) resumes on a fresh pod when the user has rendered episode shots downloaded.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3279,7 +3279,8 @@
         <is>
           <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).
 Status (2026-04-27): SHIPPED. 91 Node 7 tests pass (47 Phase 1 + 44 Phase 2; 436 repo-wide, zero regressions). Wired XLabs Flux IP-Adapter v2 into workflow_flux_v2.json via 3 additive locked node IDs: 22 ('Load Flux IPAdatpter' [sic - upstream typo preserved verbatim because that's the registered class_type], 23 (LoadImage for the reference COLOR crop from Node 6E), 24 ('Apply Flux IPAdapter'). Only existing-node change is KSampler's model input rewiring from node 20 (style LoRA output) to node 24 (IP-Adapter wrapped model). ip_scale=0.8 per locked decision #6 (XLabs default is 0.93; we trade a bit of identity strength for slightly looser pose adherence -- better for varied keyposes across a shot). Reference image is the COLOR crop, NOT the DoG line-art crop, per locked decision #4. models.json gained 2 new weight pins: flux-ip-adapter-v2.safetensors (~1 GB at models/ipadapter-flux/) and clip-vit-large-patch14.safetensors (~600 MB at models/clip_vision/ for the IP-Adapter's vision encoder; distinct from the Phase 2a clip_l text encoder). models.json customNodes also gained the x-flux-comfyui clone from XLabs-AI. orchestrate.py gained NODE_FLUX_IPADAPTER_LOADER/_REF_IMAGE/_APPLY constants + parameterizer wires task.referenceColorCropPath into node 23 + re-asserts ip_scale = V2_STRENGTH_IP_ADAPTER. 7 new tests cover the shipped-JSON regression (IP-Adapter nodes present + correct class_type strings with typos + KSampler rewired to node 24 + IP-Adapter Apply inputs wired correctly), parameterizer behaviour (reference color -&gt; node 23, ip_scale -&gt; V2_STRENGTH_IP_ADAPTER, rough-vs-reference path-swap guard), and fail-loud regression (missing IP-Adapter node raises WorkflowTemplateError). Phase 2c is the next ship-checklist step -- switch workflow_flux_v2.json from txt2img to img2img + flip --workflow default from v1 to v2.
-Phase 2d-fixup (2026-04-27, post-live-pod-debug): Live-pod verification on a fresh A100 80GB caught two real bugs in Phase 2b's ship that would have blocked Phase 2d-run / Phase 2e-run when actually invoking ComfyUI's HTTP API. (1) workflow_flux_v2.json had class_type 'Load Flux IPAdatpter' and 'Apply Flux IPAdapter' on nodes 22 + 24. ComfyUI's /object_info reported those classes NOT registered — but 'LoadFluxIPAdapter' and 'ApplyFluxIPAdapter' (no spaces, no typo) WERE registered. Phase 2b's agent research confused upstream's NODE_CLASS_MAPPINGS keys (the internal class names ComfyUI's wire format uses) with NODE_DISPLAY_NAME_MAPPINGS values (the GUI menu labels, where the 'IPAdatpter' typo lives). Workflow JSON's class_type field uses the keys, not the values. (2) models.json IP-Adapter destination 'models/ipadapter-flux/' was wrong — x-flux-comfyui's folder_paths.folder_names_and_paths['xlabs_ipadapters'] registration scans 'models/xlabs/ipadapters/' (os.path.join(models_dir, 'xlabs', 'ipadapters')). Files in the wrong dir never appear in LoadFluxIPAdapter's ipadatper field. Phase 2d-fixup corrects: workflow_flux_v2.json class_type strings + file-level _comment; models.json destination + both role descriptions; orchestrate.py NODE_FLUX_IPADAPTER_LOADER comment + _require_node human-name strings; tests/test_node7.py pinned strings (test_shipped_workflow_flux_v2_ipadapter_class_types) + _minimal_v2_template placeholder + test_v2_parameterize_missing_ipadapter_node_raises regex match; custom_nodes/node_07_pose_refiner/README.md Phase 2b row + 17-row workflow node ID table + footer note explaining wire-protocol class_type vs GUI display name distinction. The 'ipadatper' input FIELD name (typo'd) IS real and stays as-is — that's how XLabs registered the field name in LoadFluxIPAdapter.INPUT_TYPES. 449 tests pass after the fix; zero regressions. Pod was terminated to save budget; Phase 2d-run (actual TMKOC LoRA training) resumes on a fresh pod when the user has rendered episode shots downloaded.</t>
+Phase 2d-fixup (2026-04-27, post-live-pod-debug): Live-pod verification on a fresh A100 80GB caught two real bugs in Phase 2b's ship that would have blocked Phase 2d-run / Phase 2e-run when actually invoking ComfyUI's HTTP API. (1) workflow_flux_v2.json had class_type 'Load Flux IPAdatpter' and 'Apply Flux IPAdapter' on nodes 22 + 24. ComfyUI's /object_info reported those classes NOT registered — but 'LoadFluxIPAdapter' and 'ApplyFluxIPAdapter' (no spaces, no typo) WERE registered. Phase 2b's agent research confused upstream's NODE_CLASS_MAPPINGS keys (the internal class names ComfyUI's wire format uses) with NODE_DISPLAY_NAME_MAPPINGS values (the GUI menu labels, where the 'IPAdatpter' typo lives). Workflow JSON's class_type field uses the keys, not the values. (2) models.json IP-Adapter destination 'models/ipadapter-flux/' was wrong — x-flux-comfyui's folder_paths.folder_names_and_paths['xlabs_ipadapters'] registration scans 'models/xlabs/ipadapters/' (os.path.join(models_dir, 'xlabs', 'ipadapters')). Files in the wrong dir never appear in LoadFluxIPAdapter's ipadatper field. Phase 2d-fixup corrects: workflow_flux_v2.json class_type strings + file-level _comment; models.json destination + both role descriptions; orchestrate.py NODE_FLUX_IPADAPTER_LOADER comment + _require_node human-name strings; tests/test_node7.py pinned strings (test_shipped_workflow_flux_v2_ipadapter_class_types) + _minimal_v2_template placeholder + test_v2_parameterize_missing_ipadapter_node_raises regex match; custom_nodes/node_07_pose_refiner/README.md Phase 2b row + 17-row workflow node ID table + footer note explaining wire-protocol class_type vs GUI display name distinction. The 'ipadatper' input FIELD name (typo'd) IS real and stays as-is — that's how XLabs registered the field name in LoadFluxIPAdapter.INPUT_TYPES. 449 tests pass after the fix; zero regressions. Pod was terminated to save budget; Phase 2d-run (actual TMKOC LoRA training) resumes on a fresh pod when the user has rendered episode shots downloaded.
+Phase 2-revision (2026-04-28, post-design-review): Real-shot test on the Phase 2c v2 stack produced colored TMKOC scenes (via colored prompts) on whole-frame img2img output. Two design regressions caught at the same time: (1) Phase 2c implemented 'img2img on the rough crop' as VAEEncode of the WHOLE-FRAME keypose at node 50, breaking Phase 1 locked decision #5 (per-character generation, NOT whole-frame inpaint) — BG furniture and other characters got pulled into Flux's view. (2) Phase 2c prompts asked for 'flat cartoon style ... bright daytime colors' and rejected 'monochrome', biasing v2 toward color — but Part 1's locked spec is BnW line art on white. Phase 2-revision corrects three things at once: (1) `_run_one_task` pre-crops keypose to (Node-5 bbox + 20% margin) via new `_prepare_rough_bbox_crop` helper, clamped to image bounds + resized to multiples of 16 (Flux requirement) with longest edge ≤ 768; the bbox crop becomes node 50's input so pose preprocessor + VAEEncode + KSampler all operate on character-only pixels. The parameterizer accepts a new `rough_image_override` parameter so production runs pass the bbox-crop path while parameterizer-only unit tests fall back to `task.keyPosePath`. (2) `V2_POSITIVE_PROMPT_TEMPLATE` swapped from 'flat cartoon style ... bright daytime colors' → 'clean black ink line art ... white background, no fill, no color'. `V2_NEGATIVE_PROMPT` swapped from rejecting 'monochrome' → rejecting 'color, fill, shading, scene, furniture'. The negative no longer rejects 'monochrome' (Phase 2c's bug — that was rejecting exactly what Part 1 wants). (3) New `STYLE_LORA_STRENGTHS` per-LoRA strength table — `flat_cartoon_v12 → 0.0` (LoRA loads but is bypassed because it biases toward color, conflicting with Part 1's BnW deliverable; LoraLoader can't be skipped without rewiring nodes 30 + 24), `tmkoc_v1 → 0.75` (locked decision #2 production value, applied automatically once Phase 2d-run ships the custom-trained LINE-ART LoRA). Locked decision #2 ("style LoRA at 0.75") survives intact for the LoRA we actually want to use. `workflow_flux_v2.json` node 20 strength updated to 0.0 in JSON; `V2_STYLE_LORA_STRENGTH` constant retained for backwards compat. Phase 2d training-data approach also flipped: PHASE2D_TRAINING_PLAYBOOK.md revised end-to-end from synthetic Path A bootstrap → user's storyboard scene cuts directly (clean BnW digital lines on white BG; already in the target aesthetic; per-iteration cost drops from ~$10-15 + 12-18 hrs to ~$3-5 + 4-8 hrs). 9 new tests + 2 modified tests cover the per-LoRA strength table + BnW prompt assertions + bbox-crop helper + rough_image_override mechanism + regression guards on the shipped JSON's node 20 strength=0.0. Net effect: v2's deliverable now matches Phase 1's deliverable shape (per-character BnW line-art PNGs Node 8 composites onto a white-BG frame at bbox positions), but with Flux's superior generation quality + character identity preservation via XLabs IP-Adapter. The 14 original Phase 2 locked decisions stand; Phase 2-revision corrects the implementation regression that contradicted decisions #4 + #5 and Part 1's BnW deliverable.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +127,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1600,9 +1603,10 @@
           <t>scipy.ndimage.label + binary_erosion (classical CC); numpy (Otsu); Pillow (PNG load). No ML, no GPU.</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Locked 2026-04-23: classical CC over ML (no 2GB download per pod; line-art doesn't fit ML training distribution); per-key-pose detection (not per-shot); position bins 25/20/10/20/25 split; Strategy A positional identity zip (v1); warn AND reconcile on count mismatch.</t>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Locked 2026-04-23: classical CC over ML (no 2GB download per pod; line-art doesn't fit ML training distribution); per-key-pose detection (not per-shot); position bins 25/20/10/20/25 split; Strategy A positional identity zip (v1); warn AND reconcile on count mismatch.
+Phase 2f (2026-04-28, post-real-shot-debug): the user's storyboard convention puts character outlines at luminance ~0-50 (dark bold black) and BG furniture / safe-area marks at ~80-180 (light grey). The original Otsu binarization (locked decision #1, 2026-04-23) treated all dark-vs-light pixels as one foreground class, which broke when BG lines were drawn — Otsu would either swallow the actual characters into one giant connected component covering 70%+ of the frame OR falsely tag the BG as the character. Phase 2f replaces Otsu with a fixed luminance threshold (default 80, --dark-threshold N to tune) followed by 3x3 morphological closing to seal 1-2 pixel gaps where character outlines crossed BG lines. Side effect: each shot grows a &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose (white BG, black character ink). Node 7's _prepare_rough_bbox_crop reads from dark_lines/ when present (falls back to raw keypose for pre-Phase-2f work dirs), so Flux's VAEEncode + ControlNet operate on character-only pixels. Schema additions are additive: CharacterMap gains darkThreshold + darkLinesDir; Node5Result gains darkThreshold; schemaVersion stays at 1. 70 Node 5 tests pass (+20 new Phase 2f); 479 repo-wide, zero regressions. Otsu function is retained as _binarize_otsu for tests/debugging but no longer wired into _detect_on_key_pose for production.</t>
         </is>
       </c>
     </row>
@@ -1676,9 +1680,10 @@
           <t>numpy (Otsu inline); scipy.ndimage.label + find_objects</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>8-connectivity (diagonals count). Otsu is adaptive so paper/ink tone variation across shots is handled. IoU merge reunites floating details (eye drawn as separate blob) with parent silhouette.</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>8-connectivity (diagonals count). Otsu is adaptive so paper/ink tone variation across shots is handled. IoU merge reunites floating details (eye drawn as separate blob) with parent silhouette.
+Phase 2f (2026-04-28): replaced Otsu binarization with _extract_dark_lines (fixed luminance threshold, default 80) + _close_outline_gaps (3x3 morphological closing) before the CC step. Otsu is retained as _binarize_otsu for tests but no longer wired into the production path. Side-effect _save_dark_lines_png writes &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose for Node 7 to consume — gives Flux character-only pixels with BG furniture erased to white. _wipe_dark_lines_dir handles rerun safety (removes stale *.png, leaves non-PNG files alone for operator debug notes). All four helpers exported in __all__.</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3414,12 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Phase 2f — Fix Node 5 background-line detection bug (upstream prerequisite)</t>
+          <t>Phase 2f - Fix Node 5 background-line detection bug (DONE 2026-04-28)</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Real TMKOC test exposed a Node 5 failure mode: when the rough animatic has sketched background lines (panels, furniture, scene boundaries), Otsu binarization picks them up as one giant connected component covering the entire frame — a single character bbox of [0, 0, 1280, 720] for the whole key pose. Cascades into garbage Node 6 angle picks (essentially random) → wrong character generated by Node 7. Doesn't touch Node 7 directly but is an upstream prerequisite for clean Phase 2c output on real client shots.</t>
+          <t>Real TMKOC test exposed a Node 5 failure mode: when the rough animatic has sketched BG lines, Otsu binarization treated all dark-vs-light pixels as one foreground class, swallowing the actual characters or falsely tagging the BG as a giant single character. The user identified the real semantic signal: character outlines are dark bold black (~0-50 luminance) while BG furniture is light grey (~80-180). Phase 2f replaces Otsu with a fixed luminance threshold + 3x3 morphological closing.</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3424,17 +3429,18 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Modified pipeline/node5.py: Otsu fallback when bbox spans &gt;70% of frame (re-runs detection with a stricter threshold; if still oversized, splits via metadata-driven region-of-interest hints). Modified frontend/index.html to optionally capture per-shot bbox hints. Test fixture for the TMKOC background-line failure mode.</t>
+          <t>Modified pipeline/node5.py: new _extract_dark_lines + _close_outline_gaps + _save_dark_lines_png + _wipe_dark_lines_dir helpers; --dark-threshold N CLI flag; &lt;shot&gt;/dark_lines/&lt;filename&gt;.png side-effect (BnW: black ink on white BG) per keypose. Modified custom_nodes/node_07_pose_refiner/orchestrate.py: new _resolve_dark_lines_source resolver that _prepare_rough_bbox_crop calls before reading the source PNG.</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>scipy + Pillow (existing Node 5 stack); no new deps.</t>
+          <t>scipy.ndimage.binary_closing (existing Node 5 dep); Pillow (existing Node 5 dep); no new packages.</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>Out of strict Node 7 scope but blocking real Phase 2c quality verification. Schedule: ship before or alongside Phase 2c so Phase 2c's first real client validation isn't sabotaged by Node 5 garbage upstream.</t>
+          <t>Out of strict Node 7 scope but blocking real Phase 2c quality verification. Schedule: ship before or alongside Phase 2c so Phase 2c's first real client validation isn't sabotaged by Node 5 garbage upstream.
+DONE 2026-04-28. Original sketch ('Otsu fallback when bbox &gt; 70% of frame + ROI hint via metadata') was a heuristic-based size check; the user's 'dark vs light line' insight is a much better semantic signal that's actually in the artwork. 70 Node 5 tests pass (+20 new) + 114 Node 7 tests pass (+4 new); 479 repo-wide, zero regressions. Schema additions additive (CharacterMap gains darkThreshold + darkLinesDir; Node5Result gains darkThreshold; schemaVersion stays at 1) so old work dirs load unchanged. Backward-compat fallback: when &lt;shot&gt;/dark_lines/ is missing (pre-Phase-2f work dirs), Node 7 reads from the raw keypose, no migration step required.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -3285,7 +3285,8 @@
           <t>IP-Adapter strength 0.8 default per locked decision #6. Phase 2b's IP-Adapter alone may produce ~85% identity quality, sufficient for many shots without the full per-character LoRA stack from Phase 2e (which pushes to ~95%).
 Status (2026-04-27): SHIPPED. 91 Node 7 tests pass (47 Phase 1 + 44 Phase 2; 436 repo-wide, zero regressions). Wired XLabs Flux IP-Adapter v2 into workflow_flux_v2.json via 3 additive locked node IDs: 22 ('Load Flux IPAdatpter' [sic - upstream typo preserved verbatim because that's the registered class_type], 23 (LoadImage for the reference COLOR crop from Node 6E), 24 ('Apply Flux IPAdapter'). Only existing-node change is KSampler's model input rewiring from node 20 (style LoRA output) to node 24 (IP-Adapter wrapped model). ip_scale=0.8 per locked decision #6 (XLabs default is 0.93; we trade a bit of identity strength for slightly looser pose adherence -- better for varied keyposes across a shot). Reference image is the COLOR crop, NOT the DoG line-art crop, per locked decision #4. models.json gained 2 new weight pins: flux-ip-adapter-v2.safetensors (~1 GB at models/ipadapter-flux/) and clip-vit-large-patch14.safetensors (~600 MB at models/clip_vision/ for the IP-Adapter's vision encoder; distinct from the Phase 2a clip_l text encoder). models.json customNodes also gained the x-flux-comfyui clone from XLabs-AI. orchestrate.py gained NODE_FLUX_IPADAPTER_LOADER/_REF_IMAGE/_APPLY constants + parameterizer wires task.referenceColorCropPath into node 23 + re-asserts ip_scale = V2_STRENGTH_IP_ADAPTER. 7 new tests cover the shipped-JSON regression (IP-Adapter nodes present + correct class_type strings with typos + KSampler rewired to node 24 + IP-Adapter Apply inputs wired correctly), parameterizer behaviour (reference color -&gt; node 23, ip_scale -&gt; V2_STRENGTH_IP_ADAPTER, rough-vs-reference path-swap guard), and fail-loud regression (missing IP-Adapter node raises WorkflowTemplateError). Phase 2c is the next ship-checklist step -- switch workflow_flux_v2.json from txt2img to img2img + flip --workflow default from v1 to v2.
 Phase 2d-fixup (2026-04-27, post-live-pod-debug): Live-pod verification on a fresh A100 80GB caught two real bugs in Phase 2b's ship that would have blocked Phase 2d-run / Phase 2e-run when actually invoking ComfyUI's HTTP API. (1) workflow_flux_v2.json had class_type 'Load Flux IPAdatpter' and 'Apply Flux IPAdapter' on nodes 22 + 24. ComfyUI's /object_info reported those classes NOT registered — but 'LoadFluxIPAdapter' and 'ApplyFluxIPAdapter' (no spaces, no typo) WERE registered. Phase 2b's agent research confused upstream's NODE_CLASS_MAPPINGS keys (the internal class names ComfyUI's wire format uses) with NODE_DISPLAY_NAME_MAPPINGS values (the GUI menu labels, where the 'IPAdatpter' typo lives). Workflow JSON's class_type field uses the keys, not the values. (2) models.json IP-Adapter destination 'models/ipadapter-flux/' was wrong — x-flux-comfyui's folder_paths.folder_names_and_paths['xlabs_ipadapters'] registration scans 'models/xlabs/ipadapters/' (os.path.join(models_dir, 'xlabs', 'ipadapters')). Files in the wrong dir never appear in LoadFluxIPAdapter's ipadatper field. Phase 2d-fixup corrects: workflow_flux_v2.json class_type strings + file-level _comment; models.json destination + both role descriptions; orchestrate.py NODE_FLUX_IPADAPTER_LOADER comment + _require_node human-name strings; tests/test_node7.py pinned strings (test_shipped_workflow_flux_v2_ipadapter_class_types) + _minimal_v2_template placeholder + test_v2_parameterize_missing_ipadapter_node_raises regex match; custom_nodes/node_07_pose_refiner/README.md Phase 2b row + 17-row workflow node ID table + footer note explaining wire-protocol class_type vs GUI display name distinction. The 'ipadatper' input FIELD name (typo'd) IS real and stays as-is — that's how XLabs registered the field name in LoadFluxIPAdapter.INPUT_TYPES. 449 tests pass after the fix; zero regressions. Pod was terminated to save budget; Phase 2d-run (actual TMKOC LoRA training) resumes on a fresh pod when the user has rendered episode shots downloaded.
-Phase 2-revision (2026-04-28, post-design-review): Real-shot test on the Phase 2c v2 stack produced colored TMKOC scenes (via colored prompts) on whole-frame img2img output. Two design regressions caught at the same time: (1) Phase 2c implemented 'img2img on the rough crop' as VAEEncode of the WHOLE-FRAME keypose at node 50, breaking Phase 1 locked decision #5 (per-character generation, NOT whole-frame inpaint) — BG furniture and other characters got pulled into Flux's view. (2) Phase 2c prompts asked for 'flat cartoon style ... bright daytime colors' and rejected 'monochrome', biasing v2 toward color — but Part 1's locked spec is BnW line art on white. Phase 2-revision corrects three things at once: (1) `_run_one_task` pre-crops keypose to (Node-5 bbox + 20% margin) via new `_prepare_rough_bbox_crop` helper, clamped to image bounds + resized to multiples of 16 (Flux requirement) with longest edge ≤ 768; the bbox crop becomes node 50's input so pose preprocessor + VAEEncode + KSampler all operate on character-only pixels. The parameterizer accepts a new `rough_image_override` parameter so production runs pass the bbox-crop path while parameterizer-only unit tests fall back to `task.keyPosePath`. (2) `V2_POSITIVE_PROMPT_TEMPLATE` swapped from 'flat cartoon style ... bright daytime colors' → 'clean black ink line art ... white background, no fill, no color'. `V2_NEGATIVE_PROMPT` swapped from rejecting 'monochrome' → rejecting 'color, fill, shading, scene, furniture'. The negative no longer rejects 'monochrome' (Phase 2c's bug — that was rejecting exactly what Part 1 wants). (3) New `STYLE_LORA_STRENGTHS` per-LoRA strength table — `flat_cartoon_v12 → 0.0` (LoRA loads but is bypassed because it biases toward color, conflicting with Part 1's BnW deliverable; LoraLoader can't be skipped without rewiring nodes 30 + 24), `tmkoc_v1 → 0.75` (locked decision #2 production value, applied automatically once Phase 2d-run ships the custom-trained LINE-ART LoRA). Locked decision #2 ("style LoRA at 0.75") survives intact for the LoRA we actually want to use. `workflow_flux_v2.json` node 20 strength updated to 0.0 in JSON; `V2_STYLE_LORA_STRENGTH` constant retained for backwards compat. Phase 2d training-data approach also flipped: PHASE2D_TRAINING_PLAYBOOK.md revised end-to-end from synthetic Path A bootstrap → user's storyboard scene cuts directly (clean BnW digital lines on white BG; already in the target aesthetic; per-iteration cost drops from ~$10-15 + 12-18 hrs to ~$3-5 + 4-8 hrs). 9 new tests + 2 modified tests cover the per-LoRA strength table + BnW prompt assertions + bbox-crop helper + rough_image_override mechanism + regression guards on the shipped JSON's node 20 strength=0.0. Net effect: v2's deliverable now matches Phase 1's deliverable shape (per-character BnW line-art PNGs Node 8 composites onto a white-BG frame at bbox positions), but with Flux's superior generation quality + character identity preservation via XLabs IP-Adapter. The 14 original Phase 2 locked decisions stand; Phase 2-revision corrects the implementation regression that contradicted decisions #4 + #5 and Part 1's BnW deliverable.</t>
+Phase 2-revision (2026-04-28, post-design-review): Real-shot test on the Phase 2c v2 stack produced colored TMKOC scenes (via colored prompts) on whole-frame img2img output. Two design regressions caught at the same time: (1) Phase 2c implemented 'img2img on the rough crop' as VAEEncode of the WHOLE-FRAME keypose at node 50, breaking Phase 1 locked decision #5 (per-character generation, NOT whole-frame inpaint) — BG furniture and other characters got pulled into Flux's view. (2) Phase 2c prompts asked for 'flat cartoon style ... bright daytime colors' and rejected 'monochrome', biasing v2 toward color — but Part 1's locked spec is BnW line art on white. Phase 2-revision corrects three things at once: (1) `_run_one_task` pre-crops keypose to (Node-5 bbox + 20% margin) via new `_prepare_rough_bbox_crop` helper, clamped to image bounds + resized to multiples of 16 (Flux requirement) with longest edge ≤ 768; the bbox crop becomes node 50's input so pose preprocessor + VAEEncode + KSampler all operate on character-only pixels. The parameterizer accepts a new `rough_image_override` parameter so production runs pass the bbox-crop path while parameterizer-only unit tests fall back to `task.keyPosePath`. (2) `V2_POSITIVE_PROMPT_TEMPLATE` swapped from 'flat cartoon style ... bright daytime colors' → 'clean black ink line art ... white background, no fill, no color'. `V2_NEGATIVE_PROMPT` swapped from rejecting 'monochrome' → rejecting 'color, fill, shading, scene, furniture'. The negative no longer rejects 'monochrome' (Phase 2c's bug — that was rejecting exactly what Part 1 wants). (3) New `STYLE_LORA_STRENGTHS` per-LoRA strength table — `flat_cartoon_v12 → 0.0` (LoRA loads but is bypassed because it biases toward color, conflicting with Part 1's BnW deliverable; LoraLoader can't be skipped without rewiring nodes 30 + 24), `tmkoc_v1 → 0.75` (locked decision #2 production value, applied automatically once Phase 2d-run ships the custom-trained LINE-ART LoRA). Locked decision #2 ("style LoRA at 0.75") survives intact for the LoRA we actually want to use. `workflow_flux_v2.json` node 20 strength updated to 0.0 in JSON; `V2_STYLE_LORA_STRENGTH` constant retained for backwards compat. Phase 2d training-data approach also flipped: PHASE2D_TRAINING_PLAYBOOK.md revised end-to-end from synthetic Path A bootstrap → user's storyboard scene cuts directly (clean BnW digital lines on white BG; already in the target aesthetic; per-iteration cost drops from ~$10-15 + 12-18 hrs to ~$3-5 + 4-8 hrs). 9 new tests + 2 modified tests cover the per-LoRA strength table + BnW prompt assertions + bbox-crop helper + rough_image_override mechanism + regression guards on the shipped JSON's node 20 strength=0.0. Net effect: v2's deliverable now matches Phase 1's deliverable shape (per-character BnW line-art PNGs Node 8 composites onto a white-BG frame at bbox positions), but with Flux's superior generation quality + character identity preservation via XLabs IP-Adapter. The 14 original Phase 2 locked decisions stand; Phase 2-revision corrects the implementation regression that contradicted decisions #4 + #5 and Part 1's BnW deliverable.
+Phase 2-revision-fixup-1 + -fixup-2 (2026-04-28, post-live-pod-debug): live smoke on a fresh A100 80GB caught two bugs the dry-run + parameterizer-only unit tests missed because they only manifest on the live _run_one_task non-dry-run path that contacts ComfyUI's HTTP API. (1) orchestrate.py's Phase 2-revision bbox-crop block calls _safe_segment(task.identity) to build the per-detection crop filename; _safe_segment lives in manifest.py and orchestrate.py never imported it. Every Node 7 detection died with NameError before any ComfyUI POST. Fix: added _safe_segment to orchestrate.py's `from .manifest import (...)` block + new regression test test_orchestrate_imports_safe_segment_from_manifest. (2) workflow_flux_v2.json node 22 LoadFluxIPAdapter had `provider: "CUDA"` but x-flux-comfyui's INPUT_TYPES registers provider as ["CPU", "GPU"]; ComfyUI's prompt validator rejected every workflow with "Value not in list: provider: 'CUDA' not in ['CPU', 'GPU']". Phase 2b's agent-research used the underlying CUDA provider name instead of the dropdown value. Fix: changed to "GPU" + new regression test test_shipped_workflow_flux_v2_ipadapter_provider_is_valid. Live-pod smoke verified end-to-end through Node 7's ComfyUI submission step before the bug fired (Nodes 2-6 ran cleanly: 88 frames decoded → 3 keyposes → 6 detections → 6 reference matches; Phase 2f's &lt;shot&gt;/dark_lines/ generated 3 BnW PNGs as expected). 116 Node-7 tests pass after both fixups (114 pre-fixup + 2 new regression tests). 3rd smoke retry to visually verify per-character BnW output was BLOCKED 2026-04-28 by RunPod credit exhaustion; resume with credit recharge.</t>
         </is>
       </c>
     </row>

--- a/docs/Node_Plan.xlsx
+++ b/docs/Node_Plan.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7.77734375" customWidth="1" min="1" max="1"/>
@@ -1606,7 +1606,8 @@
       <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Locked 2026-04-23: classical CC over ML (no 2GB download per pod; line-art doesn't fit ML training distribution); per-key-pose detection (not per-shot); position bins 25/20/10/20/25 split; Strategy A positional identity zip (v1); warn AND reconcile on count mismatch.
-Phase 2f (2026-04-28, post-real-shot-debug): the user's storyboard convention puts character outlines at luminance ~0-50 (dark bold black) and BG furniture / safe-area marks at ~80-180 (light grey). The original Otsu binarization (locked decision #1, 2026-04-23) treated all dark-vs-light pixels as one foreground class, which broke when BG lines were drawn — Otsu would either swallow the actual characters into one giant connected component covering 70%+ of the frame OR falsely tag the BG as the character. Phase 2f replaces Otsu with a fixed luminance threshold (default 80, --dark-threshold N to tune) followed by 3x3 morphological closing to seal 1-2 pixel gaps where character outlines crossed BG lines. Side effect: each shot grows a &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose (white BG, black character ink). Node 7's _prepare_rough_bbox_crop reads from dark_lines/ when present (falls back to raw keypose for pre-Phase-2f work dirs), so Flux's VAEEncode + ControlNet operate on character-only pixels. Schema additions are additive: CharacterMap gains darkThreshold + darkLinesDir; Node5Result gains darkThreshold; schemaVersion stays at 1. 70 Node 5 tests pass (+20 new Phase 2f); 479 repo-wide, zero regressions. Otsu function is retained as _binarize_otsu for tests/debugging but no longer wired into _detect_on_key_pose for production.</t>
+Phase 2f (2026-04-28, post-real-shot-debug): the user's storyboard convention puts character outlines at luminance ~0-50 (dark bold black) and BG furniture / safe-area marks at ~80-180 (light grey). The original Otsu binarization (locked decision #1, 2026-04-23) treated all dark-vs-light pixels as one foreground class, which broke when BG lines were drawn — Otsu would either swallow the actual characters into one giant connected component covering 70%+ of the frame OR falsely tag the BG as the character. Phase 2f replaces Otsu with a fixed luminance threshold (default 80, --dark-threshold N to tune) followed by 3x3 morphological closing to seal 1-2 pixel gaps where character outlines crossed BG lines. Side effect: each shot grows a &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose (white BG, black character ink). Node 7's _prepare_rough_bbox_crop reads from dark_lines/ when present (falls back to raw keypose for pre-Phase-2f work dirs), so Flux's VAEEncode + ControlNet operate on character-only pixels. Schema additions are additive: CharacterMap gains darkThreshold + darkLinesDir; Node5Result gains darkThreshold; schemaVersion stays at 1. 70 Node 5 tests pass (+20 new Phase 2f); 479 repo-wide, zero regressions. Otsu function is retained as _binarize_otsu for tests/debugging but no longer wired into _detect_on_key_pose for production.
+Phase 2f-tuning (2026-05-03, post-live-pod-debug): Phase 2f's 3x3 morphological closing only sealed 1-2 pixel gaps in character outlines, but storyboard art commonly has 5-15 pixel gaps where the artist lifted the pen between strokes (head outline doesn't touch torso, arms don't connect to body). The character then fragmented into 4-6 connected components and Node 5's reconcile dropped the wrong fragments — live-pod test 2026-05-03 on TMKOC EP35 SH004 caught Node 5 detecting bbox=178 px tall (25% of frame) when the actual character was ~430 px tall (60% of frame). Phase 2f-tuning shipped _detect_bboxes_adaptive: iterative dilation BEFORE CC, trying levels [0, 1, 2, 3, 5, 7, 10, max_dilation] and stopping at the first level where significant-blob count &lt;= metadata's expected_count. Adapts naturally to camera framing — wide shots small characters need 0-2 dilations, close-ups large characters need 8-15. CLI flag --bbox-max-dilation N (default 15) caps the iteration count. New bbox-adaptive-dilation warning records the chosen level per-keypose. Schema additions are additive: CharacterMap + Node5Result gain bboxMaxDilation: int = 15 (defaults fill in for old manifests; schemaVersion stays at 1). 7 new tests; 77 total Node 5 tests; 500 repo-wide, zero regressions.</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1684,8 @@
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>8-connectivity (diagonals count). Otsu is adaptive so paper/ink tone variation across shots is handled. IoU merge reunites floating details (eye drawn as separate blob) with parent silhouette.
-Phase 2f (2026-04-28): replaced Otsu binarization with _extract_dark_lines (fixed luminance threshold, default 80) + _close_outline_gaps (3x3 morphological closing) before the CC step. Otsu is retained as _binarize_otsu for tests but no longer wired into the production path. Side-effect _save_dark_lines_png writes &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose for Node 7 to consume — gives Flux character-only pixels with BG furniture erased to white. _wipe_dark_lines_dir handles rerun safety (removes stale *.png, leaves non-PNG files alone for operator debug notes). All four helpers exported in __all__.</t>
+Phase 2f (2026-04-28): replaced Otsu binarization with _extract_dark_lines (fixed luminance threshold, default 80) + _close_outline_gaps (3x3 morphological closing) before the CC step. Otsu is retained as _binarize_otsu for tests but no longer wired into the production path. Side-effect _save_dark_lines_png writes &lt;shot&gt;/dark_lines/&lt;filename&gt;.png per keypose for Node 7 to consume — gives Flux character-only pixels with BG furniture erased to white. _wipe_dark_lines_dir handles rerun safety (removes stale *.png, leaves non-PNG files alone for operator debug notes). All four helpers exported in __all__.
+Phase 2f-tuning (2026-05-03): replaced _detect_bboxes (single dilation pass) with _detect_bboxes_adaptive (iterative dilation toward expected_count from metadata) for the production path. _detect_bboxes is retained for tests. Adapts to character size on canvas — small wide-shot characters get 0-2 dilations; large close-up characters get 8-15. CLI flag --bbox-max-dilation N (default 15) caps iteration count.</t>
         </is>
       </c>
     </row>
@@ -1833,9 +1835,10 @@
           <t>Pillow (RGBA + alpha slicing) + scipy.ndimage (CC label) + numpy (Otsu + DoG + IoU/symmetry scoring); pure-Python, CPU-only</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>Locked 2026-04-23: require alpha on sheet (fail loud); canonical 8-angle order confirmed against Bhim template; structured-fail on angleOrderConfirmed=false; classical shape-similarity (IoU + symmetry + aspect + edge density) over ML; recompute silhouette in Node 6 (no Node 5 retro-change); DoG line-art (sigma1=1.0, sigma2=2.0); per-key-pose granularity; Option C thin ComfyUI wrapper; no new Python deps; characters.js now defaults angleOrderConfirmed=true.</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Locked 2026-04-23: require alpha on sheet (fail loud); canonical 8-angle order confirmed against Bhim template; structured-fail on angleOrderConfirmed=false; classical shape-similarity (IoU + symmetry + aspect + edge density) over ML; recompute silhouette in Node 6 (no Node 5 retro-change); DoG line-art (sigma1=1.0, sigma2=2.0); per-key-pose granularity; Option C thin ComfyUI wrapper; no new Python deps; characters.js now defaults angleOrderConfirmed=true.
+Phase 2g (2026-05-03, post-live-pod-debug locked decisions): default angle_mode flipped from 'auto' (multi-signal silhouette scoring across all 8 angles) to 'front-only' (always pick 'front'). Reason: IP-Adapter needs the character's FACE for identity learning; back-view crops give it nothing useful. Live-pod test 2026-05-03 on TMKOC EP35 SH004 caught Node 6's 'auto' mode picking back-3q-R (TAPPU from behind) for a front-facing rough — silhouette IoU happened to score highest on the fragmented Node 5 silhouette. IP-Adapter then had only the back of TAPPU's head as the identity reference and produced generic bald-old-man instead of TAPPU. Multi-signal scoring is RETAINED as opt-in via --angle-mode auto. CLI flag --angle-mode {auto, front-only}. New phase2g_override marker in scoreBreakdown records when the override fires. Schema additions: Node6Result gains angleMode: str = 'front-only' (additive; schemaVersion stays at 1). 9 new tests + 1 modified angle test; 43 total Node 6 tests; 500 repo-wide, zero regressions.</t>
         </is>
       </c>
     </row>
@@ -1985,9 +1988,10 @@
           <t>numpy + Pillow</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>No ML/CLIP/pose-model in v1. Interior edge density breaks front/back silhouette tie (face lines present on front, absent on back). Weights + sigmas tuned at code-time against the Bhim smoke fixture.</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>No ML/CLIP/pose-model in v1. Interior edge density breaks front/back silhouette tie (face lines present on front, absent on back). Weights + sigmas tuned at code-time against the Bhim smoke fixture.
+Phase 2g (2026-05-03): multi-signal scorer is retained for --angle-mode auto, but production default is 'front-only' which overrides best_idx to the index of the 'front' angle in sheet_crops. Reason: IP-Adapter needs the character's face for identity learning; back-view crops produce generic character output. CLI flag --angle-mode {auto, front-only}. The override leaves a phase2g_override='front' marker in scoreBreakdown.</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3458,12 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Phase 2g — Simplify Node 6 (always pick 'front' angle when IP-Adapter handles identity)</t>
+          <t>Phase 2g - Simplify Node 6 (always pick 'front' angle when IP-Adapter handles identity) (DONE 2026-05-03)</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>When Phase 2b+ IP-Adapter handles identity correction regardless of which reference angle was passed in, Node 6's per-key-pose 8-way angle classification becomes redundant overhead. Make Node 6's angle picking optional: --angle-strategy {classical,front-only} flag, default front-only when Phase 2b is active, classical otherwise. Saves ~ms per key pose; more importantly removes a class of low-confidence angle picks that produced cascading garbage in the real-shot test.</t>
+          <t>Default angle_mode = 'front-only'. The original 2026-04-23 multi-signal silhouette scoring is RETAINED as opt-in via --angle-mode auto. Reason: IP-Adapter needs the character's FACE for identity learning; back-view crops give it nothing useful. Live-pod test 2026-05-03 caught Node 6's 'auto' picking back-3q-R for a front-facing rough -&gt; IP-Adapter saw the back of TAPPU's head -&gt; output was generic bald-old-man. Front-view always shows the character's face.</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -3469,17 +3473,92 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Modified pipeline/node6.py (front-only mode that always picks the 'front' angle from the sliced reference sheet for every detection); modified pipeline/cli_node6.py (--angle-strategy flag); test cases for both modes.</t>
+          <t>Modified pipeline/node6.py: new ANGLE_MODES + DEFAULT_ANGLE_MODE + FORCED_FRONT_ANGLE constants; angle_mode parameter threaded through match_references_for_queue + match_references_for_shot + _match_one_detection; override loop after silhouette scoring; phase2g_override marker in scoreBreakdown. CLI: pipeline/cli_node6.py + custom_nodes/node_06_reference_matcher gained --angle-mode flag. Schema: Node6Result gains angleMode: str.</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>Existing Node 6 stack (numpy + scipy + Pillow); no new deps.</t>
+          <t>scipy + Pillow (existing Node 6 deps); no new packages.</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>Optional simplification — Node 6's classical multi-signal angle picker still works and can stay the default. front-only mode is a Phase 2b+ optimization since the IP-Adapter does the identity heavy-lifting from a single reference angle just as well as from the 'best' angle.</t>
+          <t>Optional simplification — Node 6's classical multi-signal angle picker still works and can stay the default. front-only mode is a Phase 2b+ optimization since the IP-Adapter does the identity heavy-lifting from a single reference angle just as well as from the 'best' angle.
+DONE 2026-05-03. 9 new tests + 1 modified angle test; 43 total Node 6; 500 repo-wide, zero regressions. Schema additive (schemaVersion stays at 1) so old node6_result.json files load unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7v2-Tune</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2f-tuning - Adaptive iterative dilation before CC for character outline gaps (DONE 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2f's 3x3 morphological closing only seals 1-2 pixel gaps in character outlines. Storyboard art commonly has 5-15 pixel gaps where the artist lifted the pen between strokes (head outline doesn't touch torso outline, etc.). Character fragments into 4-6 CCs and Node 5's reconcile drops the wrong fragments. Live-pod test 2026-05-03 caught Node 5 detecting bbox=178 px tall when the actual character was ~430 px tall. Adaptive iteration count handles all camera framings (wide shots / medium / close-ups) automatically since metadata's expected_count is the target.</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Same Node 5 inputs (node4_result.json + queue.json) + new --bbox-max-dilation N flag (default 15).</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Modified pipeline/node5.py: new _detect_bboxes_adaptive function; bbox_max_dilation parameter threaded through detect_characters_for_queue + detect_characters_for_shot + _detect_on_key_pose. Schema: CharacterMap + Node5Result gain bboxMaxDilation field. New CLI/ComfyUI flag exposes the cap. New bbox-adaptive-dilation warning records the chosen level per-keypose.</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>scipy + numpy (existing Node 5 deps); no new packages.</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-03. 7 new tests; 77 total Node 5; 500 repo-wide, zero regressions. Adaptive algorithm: try dilation in [0, 1, 2, 3, 5, 7, 10, max_dilation], pick the level whose significant-blob count is closest to expected_count (preferring fewer dilations on ties to reduce risk of over-merging adjacent characters). Schema additive (schemaVersion stays at 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7v2-FixUp3</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Phase 2-revision-fixup-3 - runpod_setup.sh x-flux-comfyui auto-patch + Node 11 timeout passthrough + PyTorch cu13 docs (DONE 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Live-pod-debug bundle for issues that bit between Phase 2-revision and the user's 3rd live-pod smoke. (a) Recent ComfyUI core (&gt;= 0.19) calls Flux blocks with attn_mask=... kwarg but x-flux-comfyui's signatures don't declare it -&gt; TypeError on every prompt. (b) Node 11's default 600s per-prompt timeout is too short for slow Flux (CPU fallback or complex shots) -&gt; orchestrator marks every detection as error even though ComfyUI is still generating in the background. (c) PyTorch 2.4.x + cu13 driver = Flux loads to GPU memory but actual sampling falls back to CPU at 12+ min/generation.</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Modifies runpod_setup.sh, pipeline/cli_node11.py, pipeline/node11.py, tools/POD_NOTES_runpod_slim.md.</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>(a) runpod_setup.sh now sed-patches **kwargs into x-flux-comfyui's DoubleStreamBlock + SingleStreamBlock forward signatures right after git clone (idempotent). (b) Node 11 CLI gained --per-prompt-timeout SECONDS flag that passes through to Node 7 via _build_argv_for_node. (c) runpod_setup.sh warns at startup if PyTorch &lt; 2.5 detected. tools/POD_NOTES_runpod_slim.md gains a Phase 2-revision-fixup-3 section documenting all four issues (this + the missing-files git-checkout issue + the x-flux-comfyui patch + the timeout passthrough).</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>bash + sed (runpod_setup.sh); argparse (CLI); no new Python packages.</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-03. 3 new Node 11 tests for timeout passthrough; 49 total Node 11; 500 repo-wide, zero regressions. The PyTorch upgrade itself is NOT done by runpod_setup.sh (the operator must `pip install --upgrade 'torch&gt;=2.5,&lt;2.7' --index-url https://download.pytorch.org/whl/cu130` manually); the warning + docs are the actionable signal.</t>
         </is>
       </c>
     </row>
